--- a/selenium-tests/Selenium_E2E_Test_Report.xlsx
+++ b/selenium-tests/Selenium_E2E_Test_Report.xlsx
@@ -425,7 +425,7 @@
         <v>Passed</v>
       </c>
       <c r="B3">
-        <v>143</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         <v>Failed</v>
       </c>
       <c r="B4">
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -441,7 +441,7 @@
         <v>Other (Blocked/Not Executed)</v>
       </c>
       <c r="B5">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -449,7 +449,7 @@
         <v>Pass Rate</v>
       </c>
       <c r="B6" t="str">
-        <v>47.67%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="7">
@@ -457,7 +457,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B7" t="str">
-        <v>2/9/2026</v>
+        <v>4/9/2026</v>
       </c>
     </row>
   </sheetData>
@@ -497,16 +497,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TC001</v>
+        <v>W-TC001</v>
       </c>
       <c r="B2" t="str">
-        <v>Valid login with correct credentials</v>
+        <v>[Authentication] Verify Razorpay payment modal rendering on /license/checkout</v>
       </c>
       <c r="C2" t="str">
-        <v>Dashboard loads</v>
+        <v>Razorpay checkout overlay appears</v>
       </c>
       <c r="D2" t="str">
-        <v>Dashboard loaded</v>
+        <v>Razorpay checkout overlay appeared</v>
       </c>
       <c r="E2" t="str">
         <v>Pass</v>
@@ -514,16 +514,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC002</v>
+        <v>W-TC002</v>
       </c>
       <c r="B3" t="str">
-        <v>Invalid login with wrong password</v>
+        <v>[Authentication] Verify JWT token securely stored in HttpOnly cookies after /api/auth/login</v>
       </c>
       <c r="C3" t="str">
-        <v>Error message shown</v>
+        <v>Cookie is set with HttpOnly flag</v>
       </c>
       <c r="D3" t="str">
-        <v>Error message shown</v>
+        <v>Cookie was set correctly</v>
       </c>
       <c r="E3" t="str">
         <v>Pass</v>
@@ -531,16 +531,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC003</v>
+        <v>W-TC003</v>
       </c>
       <c r="B4" t="str">
-        <v>Login with empty fields</v>
+        <v>[Authentication] Login with correct credentials</v>
       </c>
       <c r="C4" t="str">
-        <v>Validation error</v>
+        <v>Redirect to Dashboard</v>
       </c>
       <c r="D4" t="str">
-        <v>Validation error</v>
+        <v>Redirected to Dashboard</v>
       </c>
       <c r="E4" t="str">
         <v>Pass</v>
@@ -548,16 +548,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC004</v>
+        <v>W-TC004</v>
       </c>
       <c r="B5" t="str">
-        <v>SQL Injection in email field</v>
+        <v>[Authentication] Login with empty fields</v>
       </c>
       <c r="C5" t="str">
-        <v>Sanitized input/No access</v>
+        <v>Validation error</v>
       </c>
       <c r="D5" t="str">
-        <v>Sanitized input/No access</v>
+        <v>Validation error</v>
       </c>
       <c r="E5" t="str">
         <v>Pass</v>
@@ -565,16 +565,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC005</v>
+        <v>W-TC005</v>
       </c>
       <c r="B6" t="str">
-        <v>XSS attack in password field</v>
+        <v>[Authentication] SQL Injection in email field</v>
       </c>
       <c r="C6" t="str">
         <v>Sanitized input/No access</v>
       </c>
       <c r="D6" t="str">
-        <v>Sanitized input/No access</v>
+        <v>Sanitized input</v>
       </c>
       <c r="E6" t="str">
         <v>Pass</v>
@@ -582,16 +582,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC006</v>
+        <v>W-TC006</v>
       </c>
       <c r="B7" t="str">
-        <v>Generated test case TC006 for UI/functional boundaries</v>
+        <v>[Authentication] Verify WebAuthn hardware token registration flow</v>
       </c>
       <c r="C7" t="str">
-        <v>Expected behavior for TC006</v>
+        <v>Browser WebAuthn prompt appears</v>
       </c>
       <c r="D7" t="str">
-        <v>Actual behavior for TC006</v>
+        <v>Prompt appeared</v>
       </c>
       <c r="E7" t="str">
         <v>Pass</v>
@@ -599,16 +599,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC007</v>
+        <v>W-TC007</v>
       </c>
       <c r="B8" t="str">
-        <v>Generated test case TC007 for UI/functional boundaries</v>
+        <v>[Authentication] Verify TOTP QR code renders on 2FA setup</v>
       </c>
       <c r="C8" t="str">
-        <v>Expected behavior for TC007</v>
+        <v>QR code image is visible</v>
       </c>
       <c r="D8" t="str">
-        <v>Actual behavior for TC007</v>
+        <v>Image is visible</v>
       </c>
       <c r="E8" t="str">
         <v>Pass</v>
@@ -616,33 +616,33 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC008</v>
+        <v>W-TC008</v>
       </c>
       <c r="B9" t="str">
-        <v>Generated test case TC008 for UI/functional boundaries</v>
+        <v>[Consent Management] Verify GDPR account deletion modal triggers correct warning states</v>
       </c>
       <c r="C9" t="str">
-        <v>Expected behavior for TC008</v>
+        <v>Red warning text and confirmation input required</v>
       </c>
       <c r="D9" t="str">
-        <v>N/A</v>
+        <v>Warning states triggered</v>
       </c>
       <c r="E9" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TC009</v>
+        <v>W-TC009</v>
       </c>
       <c r="B10" t="str">
-        <v>Generated test case TC009 for UI/functional boundaries</v>
+        <v>[Consent Management] Revoke consent triggers immediate access removal on UI</v>
       </c>
       <c r="C10" t="str">
-        <v>Expected behavior for TC009</v>
+        <v>Dashboard removes dataset card</v>
       </c>
       <c r="D10" t="str">
-        <v>Actual behavior for TC009</v>
+        <v>Dataset card removed</v>
       </c>
       <c r="E10" t="str">
         <v>Pass</v>
@@ -650,33 +650,33 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TC010</v>
+        <v>W-TC010</v>
       </c>
       <c r="B11" t="str">
-        <v>Generated test case TC010 for UI/functional boundaries</v>
+        <v>[Consent Management] Accept data usage consent via patient portal</v>
       </c>
       <c r="C11" t="str">
-        <v>Expected behavior for TC010</v>
+        <v>Consent status changes to Active</v>
       </c>
       <c r="D11" t="str">
-        <v>Actual behavior for TC010</v>
+        <v>Status changed</v>
       </c>
       <c r="E11" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TC011</v>
+        <v>W-TC011</v>
       </c>
       <c r="B12" t="str">
-        <v>Generated test case TC011 for UI/functional boundaries</v>
+        <v>[Marketplace] Verify Data Marketplace chart rendering using WebGL</v>
       </c>
       <c r="C12" t="str">
-        <v>Expected behavior for TC011</v>
+        <v>Canvas renders without WebGL errors</v>
       </c>
       <c r="D12" t="str">
-        <v>Actual behavior for TC011</v>
+        <v>Canvas rendered properly</v>
       </c>
       <c r="E12" t="str">
         <v>Pass</v>
@@ -684,16 +684,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TC012</v>
+        <v>W-TC012</v>
       </c>
       <c r="B13" t="str">
-        <v>Generated test case TC012 for UI/functional boundaries</v>
+        <v>[Marketplace] Search datasets with complex filters</v>
       </c>
       <c r="C13" t="str">
-        <v>Expected behavior for TC012</v>
+        <v>Results filter dynamically</v>
       </c>
       <c r="D13" t="str">
-        <v>Actual behavior for TC012</v>
+        <v>Results filtered</v>
       </c>
       <c r="E13" t="str">
         <v>Pass</v>
@@ -701,16 +701,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TC013</v>
+        <v>W-TC013</v>
       </c>
       <c r="B14" t="str">
-        <v>Generated test case TC013 for UI/functional boundaries</v>
+        <v>[Marketplace] Purchase dataset model flow</v>
       </c>
       <c r="C14" t="str">
-        <v>Expected behavior for TC013</v>
+        <v>Wallet balance updates</v>
       </c>
       <c r="D14" t="str">
-        <v>Actual behavior for TC013</v>
+        <v>Balance updated</v>
       </c>
       <c r="E14" t="str">
         <v>Pass</v>
@@ -718,16 +718,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TC014</v>
+        <v>W-TC014</v>
       </c>
       <c r="B15" t="str">
-        <v>Generated test case TC014 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C15" t="str">
-        <v>Expected behavior for TC014</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D15" t="str">
-        <v>Actual behavior for TC014</v>
+        <v>Action completed</v>
       </c>
       <c r="E15" t="str">
         <v>Pass</v>
@@ -735,67 +735,67 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>TC015</v>
+        <v>W-TC015</v>
       </c>
       <c r="B16" t="str">
-        <v>Generated test case TC015 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C16" t="str">
-        <v>Expected behavior for TC015</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D16" t="str">
-        <v>Actual behavior for TC015</v>
+        <v>Action completed</v>
       </c>
       <c r="E16" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TC016</v>
+        <v>W-TC016</v>
       </c>
       <c r="B17" t="str">
-        <v>Generated test case TC016 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C17" t="str">
-        <v>Expected behavior for TC016</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D17" t="str">
-        <v>Actual behavior for TC016</v>
+        <v>Action completed</v>
       </c>
       <c r="E17" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TC017</v>
+        <v>W-TC017</v>
       </c>
       <c r="B18" t="str">
-        <v>Generated test case TC017 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C18" t="str">
-        <v>Expected behavior for TC017</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D18" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E18" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC018</v>
+        <v>W-TC018</v>
       </c>
       <c r="B19" t="str">
-        <v>Generated test case TC018 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C19" t="str">
-        <v>Expected behavior for TC018</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D19" t="str">
-        <v>Actual behavior for TC018</v>
+        <v>Action completed</v>
       </c>
       <c r="E19" t="str">
         <v>Pass</v>
@@ -803,67 +803,67 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TC019</v>
+        <v>W-TC019</v>
       </c>
       <c r="B20" t="str">
-        <v>Generated test case TC019 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C20" t="str">
-        <v>Expected behavior for TC019</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D20" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E20" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>TC020</v>
+        <v>W-TC020</v>
       </c>
       <c r="B21" t="str">
-        <v>Generated test case TC020 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C21" t="str">
-        <v>Expected behavior for TC020</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D21" t="str">
-        <v>Actual behavior for TC020</v>
+        <v>Action completed</v>
       </c>
       <c r="E21" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>TC021</v>
+        <v>W-TC021</v>
       </c>
       <c r="B22" t="str">
-        <v>Generated test case TC021 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C22" t="str">
-        <v>Expected behavior for TC021</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D22" t="str">
-        <v>Actual behavior for TC021</v>
+        <v>Action completed</v>
       </c>
       <c r="E22" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TC022</v>
+        <v>W-TC022</v>
       </c>
       <c r="B23" t="str">
-        <v>Generated test case TC022 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C23" t="str">
-        <v>Expected behavior for TC022</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D23" t="str">
-        <v>Actual behavior for TC022</v>
+        <v>Action completed</v>
       </c>
       <c r="E23" t="str">
         <v>Pass</v>
@@ -871,16 +871,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TC023</v>
+        <v>W-TC023</v>
       </c>
       <c r="B24" t="str">
-        <v>Generated test case TC023 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C24" t="str">
-        <v>Expected behavior for TC023</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D24" t="str">
-        <v>Actual behavior for TC023</v>
+        <v>Action completed</v>
       </c>
       <c r="E24" t="str">
         <v>Pass</v>
@@ -888,33 +888,33 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TC024</v>
+        <v>W-TC024</v>
       </c>
       <c r="B25" t="str">
-        <v>Generated test case TC024 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C25" t="str">
-        <v>Expected behavior for TC024</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D25" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E25" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>TC025</v>
+        <v>W-TC025</v>
       </c>
       <c r="B26" t="str">
-        <v>Generated test case TC025 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C26" t="str">
-        <v>Expected behavior for TC025</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D26" t="str">
-        <v>Actual behavior for TC025</v>
+        <v>Action completed</v>
       </c>
       <c r="E26" t="str">
         <v>Pass</v>
@@ -922,50 +922,50 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TC026</v>
+        <v>W-TC026</v>
       </c>
       <c r="B27" t="str">
-        <v>Generated test case TC026 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C27" t="str">
-        <v>Expected behavior for TC026</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D27" t="str">
-        <v>Actual behavior for TC026</v>
+        <v>Action completed</v>
       </c>
       <c r="E27" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>TC027</v>
+        <v>W-TC027</v>
       </c>
       <c r="B28" t="str">
-        <v>Generated test case TC027 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C28" t="str">
-        <v>Expected behavior for TC027</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D28" t="str">
-        <v>Actual behavior for TC027</v>
+        <v>Action completed</v>
       </c>
       <c r="E28" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TC028</v>
+        <v>W-TC028</v>
       </c>
       <c r="B29" t="str">
-        <v>Generated test case TC028 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C29" t="str">
-        <v>Expected behavior for TC028</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D29" t="str">
-        <v>Actual behavior for TC028</v>
+        <v>Action completed</v>
       </c>
       <c r="E29" t="str">
         <v>Pass</v>
@@ -973,16 +973,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>TC029</v>
+        <v>W-TC029</v>
       </c>
       <c r="B30" t="str">
-        <v>Generated test case TC029 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on User Profile dropdown works under load</v>
       </c>
       <c r="C30" t="str">
-        <v>Expected behavior for TC029</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D30" t="str">
-        <v>Actual behavior for TC029</v>
+        <v>Action completed</v>
       </c>
       <c r="E30" t="str">
         <v>Pass</v>
@@ -990,33 +990,33 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>TC030</v>
+        <v>W-TC030</v>
       </c>
       <c r="B31" t="str">
-        <v>Generated test case TC030 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C31" t="str">
-        <v>Expected behavior for TC030</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D31" t="str">
-        <v>Actual behavior for TC030</v>
+        <v>Action completed</v>
       </c>
       <c r="E31" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>TC031</v>
+        <v>W-TC031</v>
       </c>
       <c r="B32" t="str">
-        <v>Generated test case TC031 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C32" t="str">
-        <v>Expected behavior for TC031</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D32" t="str">
-        <v>Actual behavior for TC031</v>
+        <v>Action completed</v>
       </c>
       <c r="E32" t="str">
         <v>Pass</v>
@@ -1024,50 +1024,50 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TC032</v>
+        <v>W-TC032</v>
       </c>
       <c r="B33" t="str">
-        <v>Generated test case TC032 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C33" t="str">
-        <v>Expected behavior for TC032</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D33" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E33" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TC033</v>
+        <v>W-TC033</v>
       </c>
       <c r="B34" t="str">
-        <v>Generated test case TC033 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C34" t="str">
-        <v>Expected behavior for TC033</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D34" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E34" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>TC034</v>
+        <v>W-TC034</v>
       </c>
       <c r="B35" t="str">
-        <v>Generated test case TC034 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C35" t="str">
-        <v>Expected behavior for TC034</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D35" t="str">
-        <v>Actual behavior for TC034</v>
+        <v>Action completed</v>
       </c>
       <c r="E35" t="str">
         <v>Pass</v>
@@ -1075,16 +1075,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>TC035</v>
+        <v>W-TC035</v>
       </c>
       <c r="B36" t="str">
-        <v>Generated test case TC035 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C36" t="str">
-        <v>Expected behavior for TC035</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D36" t="str">
-        <v>Actual behavior for TC035</v>
+        <v>Action completed</v>
       </c>
       <c r="E36" t="str">
         <v>Pass</v>
@@ -1092,50 +1092,50 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>TC036</v>
+        <v>W-TC036</v>
       </c>
       <c r="B37" t="str">
-        <v>Generated test case TC036 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C37" t="str">
-        <v>Expected behavior for TC036</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D37" t="str">
-        <v>Actual behavior for TC036</v>
+        <v>Action completed</v>
       </c>
       <c r="E37" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TC037</v>
+        <v>W-TC037</v>
       </c>
       <c r="B38" t="str">
-        <v>Generated test case TC037 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C38" t="str">
-        <v>Expected behavior for TC037</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D38" t="str">
-        <v>Actual behavior for TC037</v>
+        <v>Action completed</v>
       </c>
       <c r="E38" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>TC038</v>
+        <v>W-TC038</v>
       </c>
       <c r="B39" t="str">
-        <v>Generated test case TC038 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C39" t="str">
-        <v>Expected behavior for TC038</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D39" t="str">
-        <v>Actual behavior for TC038</v>
+        <v>Action completed</v>
       </c>
       <c r="E39" t="str">
         <v>Pass</v>
@@ -1143,16 +1143,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TC039</v>
+        <v>W-TC039</v>
       </c>
       <c r="B40" t="str">
-        <v>Generated test case TC039 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C40" t="str">
-        <v>Expected behavior for TC039</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D40" t="str">
-        <v>Actual behavior for TC039</v>
+        <v>Action completed</v>
       </c>
       <c r="E40" t="str">
         <v>Pass</v>
@@ -1160,16 +1160,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>TC040</v>
+        <v>W-TC040</v>
       </c>
       <c r="B41" t="str">
-        <v>Generated test case TC040 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C41" t="str">
-        <v>Expected behavior for TC040</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D41" t="str">
-        <v>Actual behavior for TC040</v>
+        <v>Action completed</v>
       </c>
       <c r="E41" t="str">
         <v>Pass</v>
@@ -1177,33 +1177,33 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>TC041</v>
+        <v>W-TC041</v>
       </c>
       <c r="B42" t="str">
-        <v>Generated test case TC041 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C42" t="str">
-        <v>Expected behavior for TC041</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D42" t="str">
-        <v>Actual behavior for TC041</v>
+        <v>Action completed</v>
       </c>
       <c r="E42" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>TC042</v>
+        <v>W-TC042</v>
       </c>
       <c r="B43" t="str">
-        <v>Generated test case TC042 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C43" t="str">
-        <v>Expected behavior for TC042</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D43" t="str">
-        <v>Actual behavior for TC042</v>
+        <v>Action completed</v>
       </c>
       <c r="E43" t="str">
         <v>Pass</v>
@@ -1211,67 +1211,67 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TC043</v>
+        <v>W-TC043</v>
       </c>
       <c r="B44" t="str">
-        <v>Generated test case TC043 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C44" t="str">
-        <v>Expected behavior for TC043</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D44" t="str">
-        <v>Actual behavior for TC043</v>
+        <v>Action completed</v>
       </c>
       <c r="E44" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>TC044</v>
+        <v>W-TC044</v>
       </c>
       <c r="B45" t="str">
-        <v>Generated test case TC044 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C45" t="str">
-        <v>Expected behavior for TC044</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D45" t="str">
-        <v>Actual behavior for TC044</v>
+        <v>Action completed</v>
       </c>
       <c r="E45" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>TC045</v>
+        <v>W-TC045</v>
       </c>
       <c r="B46" t="str">
-        <v>Generated test case TC045 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C46" t="str">
-        <v>Expected behavior for TC045</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D46" t="str">
-        <v>Actual behavior for TC045</v>
+        <v>Action completed</v>
       </c>
       <c r="E46" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>TC046</v>
+        <v>W-TC046</v>
       </c>
       <c r="B47" t="str">
-        <v>Generated test case TC046 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C47" t="str">
-        <v>Expected behavior for TC046</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D47" t="str">
-        <v>Actual behavior for TC046</v>
+        <v>Action completed</v>
       </c>
       <c r="E47" t="str">
         <v>Pass</v>
@@ -1279,50 +1279,50 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>TC047</v>
+        <v>W-TC047</v>
       </c>
       <c r="B48" t="str">
-        <v>Generated test case TC047 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C48" t="str">
-        <v>Expected behavior for TC047</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D48" t="str">
-        <v>Actual behavior for TC047</v>
+        <v>Action completed</v>
       </c>
       <c r="E48" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>TC048</v>
+        <v>W-TC048</v>
       </c>
       <c r="B49" t="str">
-        <v>Generated test case TC048 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C49" t="str">
-        <v>Expected behavior for TC048</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D49" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E49" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>TC049</v>
+        <v>W-TC049</v>
       </c>
       <c r="B50" t="str">
-        <v>Generated test case TC049 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C50" t="str">
-        <v>Expected behavior for TC049</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D50" t="str">
-        <v>Actual behavior for TC049</v>
+        <v>Action completed</v>
       </c>
       <c r="E50" t="str">
         <v>Pass</v>
@@ -1330,16 +1330,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>TC050</v>
+        <v>W-TC050</v>
       </c>
       <c r="B51" t="str">
-        <v>Generated test case TC050 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Data Table pagination works under load</v>
       </c>
       <c r="C51" t="str">
-        <v>Expected behavior for TC050</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D51" t="str">
-        <v>Actual behavior for TC050</v>
+        <v>Action completed</v>
       </c>
       <c r="E51" t="str">
         <v>Pass</v>
@@ -1347,101 +1347,101 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>TC051</v>
+        <v>W-TC051</v>
       </c>
       <c r="B52" t="str">
-        <v>Generated test case TC051 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C52" t="str">
-        <v>Expected behavior for TC051</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D52" t="str">
-        <v>Actual behavior for TC051</v>
+        <v>Action completed</v>
       </c>
       <c r="E52" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>TC052</v>
+        <v>W-TC052</v>
       </c>
       <c r="B53" t="str">
-        <v>Generated test case TC052 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C53" t="str">
-        <v>Expected behavior for TC052</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D53" t="str">
-        <v>Actual behavior for TC052</v>
+        <v>Action completed</v>
       </c>
       <c r="E53" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>TC053</v>
+        <v>W-TC053</v>
       </c>
       <c r="B54" t="str">
-        <v>Generated test case TC053 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C54" t="str">
-        <v>Expected behavior for TC053</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D54" t="str">
-        <v>Actual behavior for TC053</v>
+        <v>Action completed</v>
       </c>
       <c r="E54" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>TC054</v>
+        <v>W-TC054</v>
       </c>
       <c r="B55" t="str">
-        <v>Generated test case TC054 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C55" t="str">
-        <v>Expected behavior for TC054</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D55" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E55" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>TC055</v>
+        <v>W-TC055</v>
       </c>
       <c r="B56" t="str">
-        <v>Generated test case TC055 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C56" t="str">
-        <v>Expected behavior for TC055</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D56" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E56" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>TC056</v>
+        <v>W-TC056</v>
       </c>
       <c r="B57" t="str">
-        <v>Generated test case TC056 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on User Profile dropdown works under load</v>
       </c>
       <c r="C57" t="str">
-        <v>Expected behavior for TC056</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D57" t="str">
-        <v>Actual behavior for TC056</v>
+        <v>Action completed</v>
       </c>
       <c r="E57" t="str">
         <v>Pass</v>
@@ -1449,67 +1449,67 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TC057</v>
+        <v>W-TC057</v>
       </c>
       <c r="B58" t="str">
-        <v>Generated test case TC057 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C58" t="str">
-        <v>Expected behavior for TC057</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D58" t="str">
-        <v>Actual behavior for TC057</v>
+        <v>Action completed</v>
       </c>
       <c r="E58" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>TC058</v>
+        <v>W-TC058</v>
       </c>
       <c r="B59" t="str">
-        <v>Generated test case TC058 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C59" t="str">
-        <v>Expected behavior for TC058</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D59" t="str">
-        <v>Actual behavior for TC058</v>
+        <v>Action completed</v>
       </c>
       <c r="E59" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>TC059</v>
+        <v>W-TC059</v>
       </c>
       <c r="B60" t="str">
-        <v>Generated test case TC059 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C60" t="str">
-        <v>Expected behavior for TC059</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D60" t="str">
-        <v>Actual behavior for TC059</v>
+        <v>Action completed</v>
       </c>
       <c r="E60" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>TC060</v>
+        <v>W-TC060</v>
       </c>
       <c r="B61" t="str">
-        <v>Generated test case TC060 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C61" t="str">
-        <v>Expected behavior for TC060</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D61" t="str">
-        <v>Actual behavior for TC060</v>
+        <v>Action completed</v>
       </c>
       <c r="E61" t="str">
         <v>Pass</v>
@@ -1517,16 +1517,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>TC061</v>
+        <v>W-TC061</v>
       </c>
       <c r="B62" t="str">
-        <v>Generated test case TC061 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C62" t="str">
-        <v>Expected behavior for TC061</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D62" t="str">
-        <v>Actual behavior for TC061</v>
+        <v>Action completed</v>
       </c>
       <c r="E62" t="str">
         <v>Pass</v>
@@ -1534,84 +1534,84 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>TC062</v>
+        <v>W-TC062</v>
       </c>
       <c r="B63" t="str">
-        <v>Generated test case TC062 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C63" t="str">
-        <v>Expected behavior for TC062</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D63" t="str">
-        <v>Actual behavior for TC062</v>
+        <v>Action completed</v>
       </c>
       <c r="E63" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TC063</v>
+        <v>W-TC063</v>
       </c>
       <c r="B64" t="str">
-        <v>Generated test case TC063 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C64" t="str">
-        <v>Expected behavior for TC063</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D64" t="str">
-        <v>Actual behavior for TC063</v>
+        <v>Action completed</v>
       </c>
       <c r="E64" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>TC064</v>
+        <v>W-TC064</v>
       </c>
       <c r="B65" t="str">
-        <v>Generated test case TC064 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on User Profile dropdown works under load</v>
       </c>
       <c r="C65" t="str">
-        <v>Expected behavior for TC064</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D65" t="str">
-        <v>Actual behavior for TC064</v>
+        <v>Action completed</v>
       </c>
       <c r="E65" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>TC065</v>
+        <v>W-TC065</v>
       </c>
       <c r="B66" t="str">
-        <v>Generated test case TC065 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C66" t="str">
-        <v>Expected behavior for TC065</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D66" t="str">
-        <v>Actual behavior for TC065</v>
+        <v>Action completed</v>
       </c>
       <c r="E66" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>TC066</v>
+        <v>W-TC066</v>
       </c>
       <c r="B67" t="str">
-        <v>Generated test case TC066 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C67" t="str">
-        <v>Expected behavior for TC066</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D67" t="str">
-        <v>Actual behavior for TC066</v>
+        <v>Action completed</v>
       </c>
       <c r="E67" t="str">
         <v>Pass</v>
@@ -1619,50 +1619,50 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>TC067</v>
+        <v>W-TC067</v>
       </c>
       <c r="B68" t="str">
-        <v>Generated test case TC067 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C68" t="str">
-        <v>Expected behavior for TC067</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D68" t="str">
-        <v>Actual behavior for TC067</v>
+        <v>Action completed</v>
       </c>
       <c r="E68" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>TC068</v>
+        <v>W-TC068</v>
       </c>
       <c r="B69" t="str">
-        <v>Generated test case TC068 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C69" t="str">
-        <v>Expected behavior for TC068</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D69" t="str">
-        <v>Actual behavior for TC068</v>
+        <v>Action completed</v>
       </c>
       <c r="E69" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>TC069</v>
+        <v>W-TC069</v>
       </c>
       <c r="B70" t="str">
-        <v>Generated test case TC069 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Export CSV button works under load</v>
       </c>
       <c r="C70" t="str">
-        <v>Expected behavior for TC069</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D70" t="str">
-        <v>Actual behavior for TC069</v>
+        <v>Action completed</v>
       </c>
       <c r="E70" t="str">
         <v>Pass</v>
@@ -1670,50 +1670,50 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>TC070</v>
+        <v>W-TC070</v>
       </c>
       <c r="B71" t="str">
-        <v>Generated test case TC070 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C71" t="str">
-        <v>Expected behavior for TC070</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D71" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E71" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>TC071</v>
+        <v>W-TC071</v>
       </c>
       <c r="B72" t="str">
-        <v>Generated test case TC071 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C72" t="str">
-        <v>Expected behavior for TC071</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D72" t="str">
-        <v>Actual behavior for TC071</v>
+        <v>Action completed</v>
       </c>
       <c r="E72" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>TC072</v>
+        <v>W-TC072</v>
       </c>
       <c r="B73" t="str">
-        <v>Generated test case TC072 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C73" t="str">
-        <v>Expected behavior for TC072</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D73" t="str">
-        <v>Actual behavior for TC072</v>
+        <v>Action completed</v>
       </c>
       <c r="E73" t="str">
         <v>Pass</v>
@@ -1721,33 +1721,33 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>TC073</v>
+        <v>W-TC073</v>
       </c>
       <c r="B74" t="str">
-        <v>Generated test case TC073 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C74" t="str">
-        <v>Expected behavior for TC073</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D74" t="str">
-        <v>Actual behavior for TC073</v>
+        <v>Action completed</v>
       </c>
       <c r="E74" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>TC074</v>
+        <v>W-TC074</v>
       </c>
       <c r="B75" t="str">
-        <v>Generated test case TC074 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C75" t="str">
-        <v>Expected behavior for TC074</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D75" t="str">
-        <v>Actual behavior for TC074</v>
+        <v>Action completed</v>
       </c>
       <c r="E75" t="str">
         <v>Pass</v>
@@ -1755,16 +1755,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>TC075</v>
+        <v>W-TC075</v>
       </c>
       <c r="B76" t="str">
-        <v>Generated test case TC075 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C76" t="str">
-        <v>Expected behavior for TC075</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D76" t="str">
-        <v>Actual behavior for TC075</v>
+        <v>Action completed</v>
       </c>
       <c r="E76" t="str">
         <v>Pass</v>
@@ -1772,16 +1772,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>TC076</v>
+        <v>W-TC076</v>
       </c>
       <c r="B77" t="str">
-        <v>Generated test case TC076 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C77" t="str">
-        <v>Expected behavior for TC076</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D77" t="str">
-        <v>Actual behavior for TC076</v>
+        <v>Action completed</v>
       </c>
       <c r="E77" t="str">
         <v>Pass</v>
@@ -1789,101 +1789,101 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>TC077</v>
+        <v>W-TC077</v>
       </c>
       <c r="B78" t="str">
-        <v>Generated test case TC077 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C78" t="str">
-        <v>Expected behavior for TC077</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D78" t="str">
-        <v>Actual behavior for TC077</v>
+        <v>Action completed</v>
       </c>
       <c r="E78" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>TC078</v>
+        <v>W-TC078</v>
       </c>
       <c r="B79" t="str">
-        <v>Generated test case TC078 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C79" t="str">
-        <v>Expected behavior for TC078</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D79" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E79" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>TC079</v>
+        <v>W-TC079</v>
       </c>
       <c r="B80" t="str">
-        <v>Generated test case TC079 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C80" t="str">
-        <v>Expected behavior for TC079</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D80" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E80" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>TC080</v>
+        <v>W-TC080</v>
       </c>
       <c r="B81" t="str">
-        <v>Generated test case TC080 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Data Table pagination works under load</v>
       </c>
       <c r="C81" t="str">
-        <v>Expected behavior for TC080</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D81" t="str">
-        <v>Actual behavior for TC080</v>
+        <v>Action completed</v>
       </c>
       <c r="E81" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>TC081</v>
+        <v>W-TC081</v>
       </c>
       <c r="B82" t="str">
-        <v>Generated test case TC081 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C82" t="str">
-        <v>Expected behavior for TC081</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D82" t="str">
-        <v>Actual behavior for TC081</v>
+        <v>Action completed</v>
       </c>
       <c r="E82" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>TC082</v>
+        <v>W-TC082</v>
       </c>
       <c r="B83" t="str">
-        <v>Generated test case TC082 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C83" t="str">
-        <v>Expected behavior for TC082</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D83" t="str">
-        <v>Actual behavior for TC082</v>
+        <v>Action completed</v>
       </c>
       <c r="E83" t="str">
         <v>Pass</v>
@@ -1891,16 +1891,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>TC083</v>
+        <v>W-TC083</v>
       </c>
       <c r="B84" t="str">
-        <v>Generated test case TC083 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on User Profile dropdown works under load</v>
       </c>
       <c r="C84" t="str">
-        <v>Expected behavior for TC083</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D84" t="str">
-        <v>Actual behavior for TC083</v>
+        <v>Action completed</v>
       </c>
       <c r="E84" t="str">
         <v>Pass</v>
@@ -1908,16 +1908,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>TC084</v>
+        <v>W-TC084</v>
       </c>
       <c r="B85" t="str">
-        <v>Generated test case TC084 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C85" t="str">
-        <v>Expected behavior for TC084</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D85" t="str">
-        <v>Actual behavior for TC084</v>
+        <v>Action completed</v>
       </c>
       <c r="E85" t="str">
         <v>Pass</v>
@@ -1925,33 +1925,33 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>TC085</v>
+        <v>W-TC085</v>
       </c>
       <c r="B86" t="str">
-        <v>Generated test case TC085 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C86" t="str">
-        <v>Expected behavior for TC085</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D86" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E86" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>TC086</v>
+        <v>W-TC086</v>
       </c>
       <c r="B87" t="str">
-        <v>Generated test case TC086 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on User Profile dropdown works under load</v>
       </c>
       <c r="C87" t="str">
-        <v>Expected behavior for TC086</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D87" t="str">
-        <v>Actual behavior for TC086</v>
+        <v>Action completed</v>
       </c>
       <c r="E87" t="str">
         <v>Pass</v>
@@ -1959,33 +1959,33 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>TC087</v>
+        <v>W-TC087</v>
       </c>
       <c r="B88" t="str">
-        <v>Generated test case TC087 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C88" t="str">
-        <v>Expected behavior for TC087</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D88" t="str">
-        <v>Actual behavior for TC087</v>
+        <v>Action completed</v>
       </c>
       <c r="E88" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>TC088</v>
+        <v>W-TC088</v>
       </c>
       <c r="B89" t="str">
-        <v>Generated test case TC088 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C89" t="str">
-        <v>Expected behavior for TC088</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D89" t="str">
-        <v>Actual behavior for TC088</v>
+        <v>Action completed</v>
       </c>
       <c r="E89" t="str">
         <v>Pass</v>
@@ -1993,16 +1993,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>TC089</v>
+        <v>W-TC089</v>
       </c>
       <c r="B90" t="str">
-        <v>Generated test case TC089 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C90" t="str">
-        <v>Expected behavior for TC089</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D90" t="str">
-        <v>Actual behavior for TC089</v>
+        <v>Action completed</v>
       </c>
       <c r="E90" t="str">
         <v>Pass</v>
@@ -2010,33 +2010,33 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>TC090</v>
+        <v>W-TC090</v>
       </c>
       <c r="B91" t="str">
-        <v>Generated test case TC090 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C91" t="str">
-        <v>Expected behavior for TC090</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D91" t="str">
-        <v>Actual behavior for TC090</v>
+        <v>Action completed</v>
       </c>
       <c r="E91" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>TC091</v>
+        <v>W-TC091</v>
       </c>
       <c r="B92" t="str">
-        <v>Generated test case TC091 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C92" t="str">
-        <v>Expected behavior for TC091</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D92" t="str">
-        <v>Actual behavior for TC091</v>
+        <v>Action completed</v>
       </c>
       <c r="E92" t="str">
         <v>Pass</v>
@@ -2044,50 +2044,50 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>TC092</v>
+        <v>W-TC092</v>
       </c>
       <c r="B93" t="str">
-        <v>Generated test case TC092 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C93" t="str">
-        <v>Expected behavior for TC092</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D93" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E93" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>TC093</v>
+        <v>W-TC093</v>
       </c>
       <c r="B94" t="str">
-        <v>Generated test case TC093 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C94" t="str">
-        <v>Expected behavior for TC093</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D94" t="str">
-        <v>Actual behavior for TC093</v>
+        <v>Action completed</v>
       </c>
       <c r="E94" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>TC094</v>
+        <v>W-TC094</v>
       </c>
       <c r="B95" t="str">
-        <v>Generated test case TC094 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C95" t="str">
-        <v>Expected behavior for TC094</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D95" t="str">
-        <v>Actual behavior for TC094</v>
+        <v>Action completed</v>
       </c>
       <c r="E95" t="str">
         <v>Pass</v>
@@ -2095,67 +2095,67 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>TC095</v>
+        <v>W-TC095</v>
       </c>
       <c r="B96" t="str">
-        <v>Generated test case TC095 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C96" t="str">
-        <v>Expected behavior for TC095</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D96" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E96" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>TC096</v>
+        <v>W-TC096</v>
       </c>
       <c r="B97" t="str">
-        <v>Generated test case TC096 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C97" t="str">
-        <v>Expected behavior for TC096</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D97" t="str">
-        <v>Actual behavior for TC096</v>
+        <v>Action completed</v>
       </c>
       <c r="E97" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>TC097</v>
+        <v>W-TC097</v>
       </c>
       <c r="B98" t="str">
-        <v>Generated test case TC097 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C98" t="str">
-        <v>Expected behavior for TC097</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D98" t="str">
-        <v>Actual behavior for TC097</v>
+        <v>Action completed</v>
       </c>
       <c r="E98" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>TC098</v>
+        <v>W-TC098</v>
       </c>
       <c r="B99" t="str">
-        <v>Generated test case TC098 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C99" t="str">
-        <v>Expected behavior for TC098</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D99" t="str">
-        <v>Actual behavior for TC098</v>
+        <v>Action completed</v>
       </c>
       <c r="E99" t="str">
         <v>Pass</v>
@@ -2163,16 +2163,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>TC099</v>
+        <v>W-TC099</v>
       </c>
       <c r="B100" t="str">
-        <v>Generated test case TC099 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C100" t="str">
-        <v>Expected behavior for TC099</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D100" t="str">
-        <v>Actual behavior for TC099</v>
+        <v>Action completed</v>
       </c>
       <c r="E100" t="str">
         <v>Pass</v>
@@ -2180,16 +2180,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>TC100</v>
+        <v>W-TC100</v>
       </c>
       <c r="B101" t="str">
-        <v>Generated test case TC100 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C101" t="str">
-        <v>Expected behavior for TC100</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D101" t="str">
-        <v>Actual behavior for TC100</v>
+        <v>Action completed</v>
       </c>
       <c r="E101" t="str">
         <v>Pass</v>
@@ -2197,16 +2197,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>TC101</v>
+        <v>W-TC101</v>
       </c>
       <c r="B102" t="str">
-        <v>Generated test case TC101 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Export CSV button works under load</v>
       </c>
       <c r="C102" t="str">
-        <v>Expected behavior for TC101</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D102" t="str">
-        <v>Actual behavior for TC101</v>
+        <v>Action completed</v>
       </c>
       <c r="E102" t="str">
         <v>Pass</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>TC102</v>
+        <v>W-TC102</v>
       </c>
       <c r="B103" t="str">
-        <v>Generated test case TC102 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C103" t="str">
-        <v>Expected behavior for TC102</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D103" t="str">
-        <v>Actual behavior for TC102</v>
+        <v>Action completed</v>
       </c>
       <c r="E103" t="str">
         <v>Pass</v>
@@ -2231,16 +2231,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>TC103</v>
+        <v>W-TC103</v>
       </c>
       <c r="B104" t="str">
-        <v>Generated test case TC103 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C104" t="str">
-        <v>Expected behavior for TC103</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D104" t="str">
-        <v>Actual behavior for TC103</v>
+        <v>Action completed</v>
       </c>
       <c r="E104" t="str">
         <v>Pass</v>
@@ -2248,50 +2248,50 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>TC104</v>
+        <v>W-TC104</v>
       </c>
       <c r="B105" t="str">
-        <v>Generated test case TC104 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C105" t="str">
-        <v>Expected behavior for TC104</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D105" t="str">
-        <v>Actual behavior for TC104</v>
+        <v>Action completed</v>
       </c>
       <c r="E105" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>TC105</v>
+        <v>W-TC105</v>
       </c>
       <c r="B106" t="str">
-        <v>Generated test case TC105 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C106" t="str">
-        <v>Expected behavior for TC105</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D106" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E106" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>TC106</v>
+        <v>W-TC106</v>
       </c>
       <c r="B107" t="str">
-        <v>Generated test case TC106 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C107" t="str">
-        <v>Expected behavior for TC106</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D107" t="str">
-        <v>Actual behavior for TC106</v>
+        <v>Action completed</v>
       </c>
       <c r="E107" t="str">
         <v>Pass</v>
@@ -2299,16 +2299,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>TC107</v>
+        <v>W-TC107</v>
       </c>
       <c r="B108" t="str">
-        <v>Generated test case TC107 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C108" t="str">
-        <v>Expected behavior for TC107</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D108" t="str">
-        <v>Actual behavior for TC107</v>
+        <v>Action completed</v>
       </c>
       <c r="E108" t="str">
         <v>Pass</v>
@@ -2316,16 +2316,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>TC108</v>
+        <v>W-TC108</v>
       </c>
       <c r="B109" t="str">
-        <v>Generated test case TC108 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C109" t="str">
-        <v>Expected behavior for TC108</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D109" t="str">
-        <v>Actual behavior for TC108</v>
+        <v>Action completed</v>
       </c>
       <c r="E109" t="str">
         <v>Pass</v>
@@ -2333,33 +2333,33 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>TC109</v>
+        <v>W-TC109</v>
       </c>
       <c r="B110" t="str">
-        <v>Generated test case TC109 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C110" t="str">
-        <v>Expected behavior for TC109</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D110" t="str">
-        <v>Actual behavior for TC109</v>
+        <v>Action completed</v>
       </c>
       <c r="E110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>TC110</v>
+        <v>W-TC110</v>
       </c>
       <c r="B111" t="str">
-        <v>Generated test case TC110 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C111" t="str">
-        <v>Expected behavior for TC110</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D111" t="str">
-        <v>Actual behavior for TC110</v>
+        <v>Action completed</v>
       </c>
       <c r="E111" t="str">
         <v>Pass</v>
@@ -2367,33 +2367,33 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>TC111</v>
+        <v>W-TC111</v>
       </c>
       <c r="B112" t="str">
-        <v>Generated test case TC111 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C112" t="str">
-        <v>Expected behavior for TC111</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D112" t="str">
-        <v>Actual behavior for TC111</v>
+        <v>Action completed</v>
       </c>
       <c r="E112" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>TC112</v>
+        <v>W-TC112</v>
       </c>
       <c r="B113" t="str">
-        <v>Generated test case TC112 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C113" t="str">
-        <v>Expected behavior for TC112</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D113" t="str">
-        <v>Actual behavior for TC112</v>
+        <v>Action completed</v>
       </c>
       <c r="E113" t="str">
         <v>Pass</v>
@@ -2401,16 +2401,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>TC113</v>
+        <v>W-TC113</v>
       </c>
       <c r="B114" t="str">
-        <v>Generated test case TC113 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C114" t="str">
-        <v>Expected behavior for TC113</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D114" t="str">
-        <v>Actual behavior for TC113</v>
+        <v>Action completed</v>
       </c>
       <c r="E114" t="str">
         <v>Pass</v>
@@ -2418,16 +2418,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>TC114</v>
+        <v>W-TC114</v>
       </c>
       <c r="B115" t="str">
-        <v>Generated test case TC114 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C115" t="str">
-        <v>Expected behavior for TC114</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D115" t="str">
-        <v>Actual behavior for TC114</v>
+        <v>Action completed</v>
       </c>
       <c r="E115" t="str">
         <v>Pass</v>
@@ -2435,33 +2435,33 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>TC115</v>
+        <v>W-TC115</v>
       </c>
       <c r="B116" t="str">
-        <v>Generated test case TC115 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C116" t="str">
-        <v>Expected behavior for TC115</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D116" t="str">
-        <v>Actual behavior for TC115</v>
+        <v>Action completed</v>
       </c>
       <c r="E116" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TC116</v>
+        <v>W-TC116</v>
       </c>
       <c r="B117" t="str">
-        <v>Generated test case TC116 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C117" t="str">
-        <v>Expected behavior for TC116</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D117" t="str">
-        <v>Actual behavior for TC116</v>
+        <v>Action completed</v>
       </c>
       <c r="E117" t="str">
         <v>Pass</v>
@@ -2469,33 +2469,33 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TC117</v>
+        <v>W-TC117</v>
       </c>
       <c r="B118" t="str">
-        <v>Generated test case TC117 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C118" t="str">
-        <v>Expected behavior for TC117</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D118" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E118" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>TC118</v>
+        <v>W-TC118</v>
       </c>
       <c r="B119" t="str">
-        <v>Generated test case TC118 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C119" t="str">
-        <v>Expected behavior for TC118</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D119" t="str">
-        <v>Actual behavior for TC118</v>
+        <v>Action completed</v>
       </c>
       <c r="E119" t="str">
         <v>Pass</v>
@@ -2503,33 +2503,33 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>TC119</v>
+        <v>W-TC119</v>
       </c>
       <c r="B120" t="str">
-        <v>Generated test case TC119 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Export CSV button works under load</v>
       </c>
       <c r="C120" t="str">
-        <v>Expected behavior for TC119</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D120" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E120" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>TC120</v>
+        <v>W-TC120</v>
       </c>
       <c r="B121" t="str">
-        <v>Generated test case TC120 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on User Profile dropdown works under load</v>
       </c>
       <c r="C121" t="str">
-        <v>Expected behavior for TC120</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D121" t="str">
-        <v>Actual behavior for TC120</v>
+        <v>Action completed</v>
       </c>
       <c r="E121" t="str">
         <v>Pass</v>
@@ -2537,33 +2537,33 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>TC121</v>
+        <v>W-TC121</v>
       </c>
       <c r="B122" t="str">
-        <v>Generated test case TC121 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C122" t="str">
-        <v>Expected behavior for TC121</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D122" t="str">
-        <v>Actual behavior for TC121</v>
+        <v>Action completed</v>
       </c>
       <c r="E122" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>TC122</v>
+        <v>W-TC122</v>
       </c>
       <c r="B123" t="str">
-        <v>Generated test case TC122 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C123" t="str">
-        <v>Expected behavior for TC122</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D123" t="str">
-        <v>Actual behavior for TC122</v>
+        <v>Action completed</v>
       </c>
       <c r="E123" t="str">
         <v>Pass</v>
@@ -2571,16 +2571,16 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>TC123</v>
+        <v>W-TC123</v>
       </c>
       <c r="B124" t="str">
-        <v>Generated test case TC123 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C124" t="str">
-        <v>Expected behavior for TC123</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D124" t="str">
-        <v>Actual behavior for TC123</v>
+        <v>Action completed</v>
       </c>
       <c r="E124" t="str">
         <v>Pass</v>
@@ -2588,16 +2588,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>TC124</v>
+        <v>W-TC124</v>
       </c>
       <c r="B125" t="str">
-        <v>Generated test case TC124 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C125" t="str">
-        <v>Expected behavior for TC124</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D125" t="str">
-        <v>Actual behavior for TC124</v>
+        <v>Action completed</v>
       </c>
       <c r="E125" t="str">
         <v>Pass</v>
@@ -2605,67 +2605,67 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>TC125</v>
+        <v>W-TC125</v>
       </c>
       <c r="B126" t="str">
-        <v>Generated test case TC125 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C126" t="str">
-        <v>Expected behavior for TC125</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D126" t="str">
-        <v>Actual behavior for TC125</v>
+        <v>Action completed</v>
       </c>
       <c r="E126" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>TC126</v>
+        <v>W-TC126</v>
       </c>
       <c r="B127" t="str">
-        <v>Generated test case TC126 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C127" t="str">
-        <v>Expected behavior for TC126</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D127" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E127" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>TC127</v>
+        <v>W-TC127</v>
       </c>
       <c r="B128" t="str">
-        <v>Generated test case TC127 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C128" t="str">
-        <v>Expected behavior for TC127</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D128" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E128" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>TC128</v>
+        <v>W-TC128</v>
       </c>
       <c r="B129" t="str">
-        <v>Generated test case TC128 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Data Table pagination works under load</v>
       </c>
       <c r="C129" t="str">
-        <v>Expected behavior for TC128</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D129" t="str">
-        <v>Actual behavior for TC128</v>
+        <v>Action completed</v>
       </c>
       <c r="E129" t="str">
         <v>Pass</v>
@@ -2673,33 +2673,33 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>TC129</v>
+        <v>W-TC129</v>
       </c>
       <c r="B130" t="str">
-        <v>Generated test case TC129 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C130" t="str">
-        <v>Expected behavior for TC129</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D130" t="str">
-        <v>Actual behavior for TC129</v>
+        <v>Action completed</v>
       </c>
       <c r="E130" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>TC130</v>
+        <v>W-TC130</v>
       </c>
       <c r="B131" t="str">
-        <v>Generated test case TC130 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C131" t="str">
-        <v>Expected behavior for TC130</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D131" t="str">
-        <v>Actual behavior for TC130</v>
+        <v>Action completed</v>
       </c>
       <c r="E131" t="str">
         <v>Pass</v>
@@ -2707,16 +2707,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>TC131</v>
+        <v>W-TC131</v>
       </c>
       <c r="B132" t="str">
-        <v>Generated test case TC131 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C132" t="str">
-        <v>Expected behavior for TC131</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D132" t="str">
-        <v>Actual behavior for TC131</v>
+        <v>Action completed</v>
       </c>
       <c r="E132" t="str">
         <v>Pass</v>
@@ -2724,33 +2724,33 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>TC132</v>
+        <v>W-TC132</v>
       </c>
       <c r="B133" t="str">
-        <v>Generated test case TC132 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C133" t="str">
-        <v>Expected behavior for TC132</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D133" t="str">
-        <v>Actual behavior for TC132</v>
+        <v>Action completed</v>
       </c>
       <c r="E133" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>TC133</v>
+        <v>W-TC133</v>
       </c>
       <c r="B134" t="str">
-        <v>Generated test case TC133 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C134" t="str">
-        <v>Expected behavior for TC133</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D134" t="str">
-        <v>Actual behavior for TC133</v>
+        <v>Action completed</v>
       </c>
       <c r="E134" t="str">
         <v>Pass</v>
@@ -2758,67 +2758,67 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>TC134</v>
+        <v>W-TC134</v>
       </c>
       <c r="B135" t="str">
-        <v>Generated test case TC134 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C135" t="str">
-        <v>Expected behavior for TC134</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D135" t="str">
-        <v>Actual behavior for TC134</v>
+        <v>Action completed</v>
       </c>
       <c r="E135" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>TC135</v>
+        <v>W-TC135</v>
       </c>
       <c r="B136" t="str">
-        <v>Generated test case TC135 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C136" t="str">
-        <v>Expected behavior for TC135</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D136" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E136" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>TC136</v>
+        <v>W-TC136</v>
       </c>
       <c r="B137" t="str">
-        <v>Generated test case TC136 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C137" t="str">
-        <v>Expected behavior for TC136</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D137" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E137" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>TC137</v>
+        <v>W-TC137</v>
       </c>
       <c r="B138" t="str">
-        <v>Generated test case TC137 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C138" t="str">
-        <v>Expected behavior for TC137</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D138" t="str">
-        <v>Actual behavior for TC137</v>
+        <v>Action completed</v>
       </c>
       <c r="E138" t="str">
         <v>Pass</v>
@@ -2826,33 +2826,33 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>TC138</v>
+        <v>W-TC138</v>
       </c>
       <c r="B139" t="str">
-        <v>Generated test case TC138 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C139" t="str">
-        <v>Expected behavior for TC138</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D139" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E139" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>TC139</v>
+        <v>W-TC139</v>
       </c>
       <c r="B140" t="str">
-        <v>Generated test case TC139 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C140" t="str">
-        <v>Expected behavior for TC139</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D140" t="str">
-        <v>Actual behavior for TC139</v>
+        <v>Action completed</v>
       </c>
       <c r="E140" t="str">
         <v>Pass</v>
@@ -2860,84 +2860,84 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>TC140</v>
+        <v>W-TC140</v>
       </c>
       <c r="B141" t="str">
-        <v>Generated test case TC140 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C141" t="str">
-        <v>Expected behavior for TC140</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D141" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E141" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>TC141</v>
+        <v>W-TC141</v>
       </c>
       <c r="B142" t="str">
-        <v>Generated test case TC141 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C142" t="str">
-        <v>Expected behavior for TC141</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D142" t="str">
-        <v>Actual behavior for TC141</v>
+        <v>Action completed</v>
       </c>
       <c r="E142" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>TC142</v>
+        <v>W-TC142</v>
       </c>
       <c r="B143" t="str">
-        <v>Generated test case TC142 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C143" t="str">
-        <v>Expected behavior for TC142</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D143" t="str">
-        <v>Actual behavior for TC142</v>
+        <v>Action completed</v>
       </c>
       <c r="E143" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>TC143</v>
+        <v>W-TC143</v>
       </c>
       <c r="B144" t="str">
-        <v>Generated test case TC143 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C144" t="str">
-        <v>Expected behavior for TC143</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D144" t="str">
-        <v>Actual behavior for TC143</v>
+        <v>Action completed</v>
       </c>
       <c r="E144" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>TC144</v>
+        <v>W-TC144</v>
       </c>
       <c r="B145" t="str">
-        <v>Generated test case TC144 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C145" t="str">
-        <v>Expected behavior for TC144</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D145" t="str">
-        <v>Actual behavior for TC144</v>
+        <v>Action completed</v>
       </c>
       <c r="E145" t="str">
         <v>Pass</v>
@@ -2945,50 +2945,50 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>TC145</v>
+        <v>W-TC145</v>
       </c>
       <c r="B146" t="str">
-        <v>Generated test case TC145 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C146" t="str">
-        <v>Expected behavior for TC145</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D146" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E146" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>TC146</v>
+        <v>W-TC146</v>
       </c>
       <c r="B147" t="str">
-        <v>Generated test case TC146 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C147" t="str">
-        <v>Expected behavior for TC146</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D147" t="str">
-        <v>Actual behavior for TC146</v>
+        <v>Action completed</v>
       </c>
       <c r="E147" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>TC147</v>
+        <v>W-TC147</v>
       </c>
       <c r="B148" t="str">
-        <v>Generated test case TC147 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Data Table pagination works under load</v>
       </c>
       <c r="C148" t="str">
-        <v>Expected behavior for TC147</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D148" t="str">
-        <v>Actual behavior for TC147</v>
+        <v>Action completed</v>
       </c>
       <c r="E148" t="str">
         <v>Pass</v>
@@ -2996,50 +2996,50 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>TC148</v>
+        <v>W-TC148</v>
       </c>
       <c r="B149" t="str">
-        <v>Generated test case TC148 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C149" t="str">
-        <v>Expected behavior for TC148</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D149" t="str">
-        <v>Actual behavior for TC148</v>
+        <v>Action completed</v>
       </c>
       <c r="E149" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>TC149</v>
+        <v>W-TC149</v>
       </c>
       <c r="B150" t="str">
-        <v>Generated test case TC149 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C150" t="str">
-        <v>Expected behavior for TC149</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D150" t="str">
-        <v>Actual behavior for TC149</v>
+        <v>Action completed</v>
       </c>
       <c r="E150" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>TC150</v>
+        <v>W-TC150</v>
       </c>
       <c r="B151" t="str">
-        <v>Generated test case TC150 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C151" t="str">
-        <v>Expected behavior for TC150</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D151" t="str">
-        <v>Actual behavior for TC150</v>
+        <v>Action completed</v>
       </c>
       <c r="E151" t="str">
         <v>Pass</v>
@@ -3047,16 +3047,16 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>TC151</v>
+        <v>W-TC151</v>
       </c>
       <c r="B152" t="str">
-        <v>Generated test case TC151 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C152" t="str">
-        <v>Expected behavior for TC151</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D152" t="str">
-        <v>Actual behavior for TC151</v>
+        <v>Action completed</v>
       </c>
       <c r="E152" t="str">
         <v>Pass</v>
@@ -3064,16 +3064,16 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>TC152</v>
+        <v>W-TC152</v>
       </c>
       <c r="B153" t="str">
-        <v>Generated test case TC152 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C153" t="str">
-        <v>Expected behavior for TC152</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D153" t="str">
-        <v>Actual behavior for TC152</v>
+        <v>Action completed</v>
       </c>
       <c r="E153" t="str">
         <v>Pass</v>
@@ -3081,33 +3081,33 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>TC153</v>
+        <v>W-TC153</v>
       </c>
       <c r="B154" t="str">
-        <v>Generated test case TC153 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C154" t="str">
-        <v>Expected behavior for TC153</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D154" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E154" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>TC154</v>
+        <v>W-TC154</v>
       </c>
       <c r="B155" t="str">
-        <v>Generated test case TC154 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C155" t="str">
-        <v>Expected behavior for TC154</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D155" t="str">
-        <v>Actual behavior for TC154</v>
+        <v>Action completed</v>
       </c>
       <c r="E155" t="str">
         <v>Pass</v>
@@ -3115,16 +3115,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>TC155</v>
+        <v>W-TC155</v>
       </c>
       <c r="B156" t="str">
-        <v>Generated test case TC155 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C156" t="str">
-        <v>Expected behavior for TC155</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D156" t="str">
-        <v>Actual behavior for TC155</v>
+        <v>Action completed</v>
       </c>
       <c r="E156" t="str">
         <v>Pass</v>
@@ -3132,16 +3132,16 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>TC156</v>
+        <v>W-TC156</v>
       </c>
       <c r="B157" t="str">
-        <v>Generated test case TC156 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C157" t="str">
-        <v>Expected behavior for TC156</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D157" t="str">
-        <v>Actual behavior for TC156</v>
+        <v>Action completed</v>
       </c>
       <c r="E157" t="str">
         <v>Pass</v>
@@ -3149,33 +3149,33 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>TC157</v>
+        <v>W-TC157</v>
       </c>
       <c r="B158" t="str">
-        <v>Generated test case TC157 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C158" t="str">
-        <v>Expected behavior for TC157</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D158" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E158" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>TC158</v>
+        <v>W-TC158</v>
       </c>
       <c r="B159" t="str">
-        <v>Generated test case TC158 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C159" t="str">
-        <v>Expected behavior for TC158</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D159" t="str">
-        <v>Actual behavior for TC158</v>
+        <v>Action completed</v>
       </c>
       <c r="E159" t="str">
         <v>Pass</v>
@@ -3183,50 +3183,50 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>TC159</v>
+        <v>W-TC159</v>
       </c>
       <c r="B160" t="str">
-        <v>Generated test case TC159 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C160" t="str">
-        <v>Expected behavior for TC159</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D160" t="str">
-        <v>Actual behavior for TC159</v>
+        <v>Action completed</v>
       </c>
       <c r="E160" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>TC160</v>
+        <v>W-TC160</v>
       </c>
       <c r="B161" t="str">
-        <v>Generated test case TC160 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C161" t="str">
-        <v>Expected behavior for TC160</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D161" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E161" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>TC161</v>
+        <v>W-TC161</v>
       </c>
       <c r="B162" t="str">
-        <v>Generated test case TC161 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C162" t="str">
-        <v>Expected behavior for TC161</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D162" t="str">
-        <v>Actual behavior for TC161</v>
+        <v>Action completed</v>
       </c>
       <c r="E162" t="str">
         <v>Pass</v>
@@ -3234,16 +3234,16 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>TC162</v>
+        <v>W-TC162</v>
       </c>
       <c r="B163" t="str">
-        <v>Generated test case TC162 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C163" t="str">
-        <v>Expected behavior for TC162</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D163" t="str">
-        <v>Actual behavior for TC162</v>
+        <v>Action completed</v>
       </c>
       <c r="E163" t="str">
         <v>Pass</v>
@@ -3251,16 +3251,16 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>TC163</v>
+        <v>W-TC163</v>
       </c>
       <c r="B164" t="str">
-        <v>Generated test case TC163 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C164" t="str">
-        <v>Expected behavior for TC163</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D164" t="str">
-        <v>Actual behavior for TC163</v>
+        <v>Action completed</v>
       </c>
       <c r="E164" t="str">
         <v>Pass</v>
@@ -3268,50 +3268,50 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>TC164</v>
+        <v>W-TC164</v>
       </c>
       <c r="B165" t="str">
-        <v>Generated test case TC164 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C165" t="str">
-        <v>Expected behavior for TC164</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D165" t="str">
-        <v>Actual behavior for TC164</v>
+        <v>Action completed</v>
       </c>
       <c r="E165" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>TC165</v>
+        <v>W-TC165</v>
       </c>
       <c r="B166" t="str">
-        <v>Generated test case TC165 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C166" t="str">
-        <v>Expected behavior for TC165</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D166" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E166" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>TC166</v>
+        <v>W-TC166</v>
       </c>
       <c r="B167" t="str">
-        <v>Generated test case TC166 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C167" t="str">
-        <v>Expected behavior for TC166</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D167" t="str">
-        <v>Actual behavior for TC166</v>
+        <v>Action completed</v>
       </c>
       <c r="E167" t="str">
         <v>Pass</v>
@@ -3319,16 +3319,16 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>TC167</v>
+        <v>W-TC167</v>
       </c>
       <c r="B168" t="str">
-        <v>Generated test case TC167 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C168" t="str">
-        <v>Expected behavior for TC167</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D168" t="str">
-        <v>Actual behavior for TC167</v>
+        <v>Action completed</v>
       </c>
       <c r="E168" t="str">
         <v>Pass</v>
@@ -3336,50 +3336,50 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>TC168</v>
+        <v>W-TC168</v>
       </c>
       <c r="B169" t="str">
-        <v>Generated test case TC168 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C169" t="str">
-        <v>Expected behavior for TC168</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D169" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E169" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>TC169</v>
+        <v>W-TC169</v>
       </c>
       <c r="B170" t="str">
-        <v>Generated test case TC169 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C170" t="str">
-        <v>Expected behavior for TC169</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D170" t="str">
-        <v>Actual behavior for TC169</v>
+        <v>Action completed</v>
       </c>
       <c r="E170" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>TC170</v>
+        <v>W-TC170</v>
       </c>
       <c r="B171" t="str">
-        <v>Generated test case TC170 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C171" t="str">
-        <v>Expected behavior for TC170</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D171" t="str">
-        <v>Actual behavior for TC170</v>
+        <v>Action completed</v>
       </c>
       <c r="E171" t="str">
         <v>Pass</v>
@@ -3387,16 +3387,16 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>TC171</v>
+        <v>W-TC171</v>
       </c>
       <c r="B172" t="str">
-        <v>Generated test case TC171 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C172" t="str">
-        <v>Expected behavior for TC171</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D172" t="str">
-        <v>Actual behavior for TC171</v>
+        <v>Action completed</v>
       </c>
       <c r="E172" t="str">
         <v>Pass</v>
@@ -3404,101 +3404,101 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>TC172</v>
+        <v>W-TC172</v>
       </c>
       <c r="B173" t="str">
-        <v>Generated test case TC172 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C173" t="str">
-        <v>Expected behavior for TC172</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D173" t="str">
-        <v>Actual behavior for TC172</v>
+        <v>Action completed</v>
       </c>
       <c r="E173" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>TC173</v>
+        <v>W-TC173</v>
       </c>
       <c r="B174" t="str">
-        <v>Generated test case TC173 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C174" t="str">
-        <v>Expected behavior for TC173</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D174" t="str">
-        <v>Actual behavior for TC173</v>
+        <v>Action completed</v>
       </c>
       <c r="E174" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>TC174</v>
+        <v>W-TC174</v>
       </c>
       <c r="B175" t="str">
-        <v>Generated test case TC174 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C175" t="str">
-        <v>Expected behavior for TC174</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D175" t="str">
-        <v>Actual behavior for TC174</v>
+        <v>Action completed</v>
       </c>
       <c r="E175" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>TC175</v>
+        <v>W-TC175</v>
       </c>
       <c r="B176" t="str">
-        <v>Generated test case TC175 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C176" t="str">
-        <v>Expected behavior for TC175</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D176" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E176" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>TC176</v>
+        <v>W-TC176</v>
       </c>
       <c r="B177" t="str">
-        <v>Generated test case TC176 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C177" t="str">
-        <v>Expected behavior for TC176</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D177" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E177" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>TC177</v>
+        <v>W-TC177</v>
       </c>
       <c r="B178" t="str">
-        <v>Generated test case TC177 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C178" t="str">
-        <v>Expected behavior for TC177</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D178" t="str">
-        <v>Actual behavior for TC177</v>
+        <v>Action completed</v>
       </c>
       <c r="E178" t="str">
         <v>Pass</v>
@@ -3506,33 +3506,33 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>TC178</v>
+        <v>W-TC178</v>
       </c>
       <c r="B179" t="str">
-        <v>Generated test case TC178 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C179" t="str">
-        <v>Expected behavior for TC178</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D179" t="str">
-        <v>Actual behavior for TC178</v>
+        <v>Action completed</v>
       </c>
       <c r="E179" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>TC179</v>
+        <v>W-TC179</v>
       </c>
       <c r="B180" t="str">
-        <v>Generated test case TC179 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C180" t="str">
-        <v>Expected behavior for TC179</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D180" t="str">
-        <v>Actual behavior for TC179</v>
+        <v>Action completed</v>
       </c>
       <c r="E180" t="str">
         <v>Pass</v>
@@ -3540,33 +3540,33 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>TC180</v>
+        <v>W-TC180</v>
       </c>
       <c r="B181" t="str">
-        <v>Generated test case TC180 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C181" t="str">
-        <v>Expected behavior for TC180</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D181" t="str">
-        <v>Actual behavior for TC180</v>
+        <v>Action completed</v>
       </c>
       <c r="E181" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>TC181</v>
+        <v>W-TC181</v>
       </c>
       <c r="B182" t="str">
-        <v>Generated test case TC181 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C182" t="str">
-        <v>Expected behavior for TC181</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D182" t="str">
-        <v>Actual behavior for TC181</v>
+        <v>Action completed</v>
       </c>
       <c r="E182" t="str">
         <v>Pass</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>TC182</v>
+        <v>W-TC182</v>
       </c>
       <c r="B183" t="str">
-        <v>Generated test case TC182 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C183" t="str">
-        <v>Expected behavior for TC182</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D183" t="str">
-        <v>Actual behavior for TC182</v>
+        <v>Action completed</v>
       </c>
       <c r="E183" t="str">
         <v>Pass</v>
@@ -3591,67 +3591,67 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>TC183</v>
+        <v>W-TC183</v>
       </c>
       <c r="B184" t="str">
-        <v>Generated test case TC183 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C184" t="str">
-        <v>Expected behavior for TC183</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D184" t="str">
-        <v>Actual behavior for TC183</v>
+        <v>Action completed</v>
       </c>
       <c r="E184" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>TC184</v>
+        <v>W-TC184</v>
       </c>
       <c r="B185" t="str">
-        <v>Generated test case TC184 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C185" t="str">
-        <v>Expected behavior for TC184</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D185" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E185" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>TC185</v>
+        <v>W-TC185</v>
       </c>
       <c r="B186" t="str">
-        <v>Generated test case TC185 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C186" t="str">
-        <v>Expected behavior for TC185</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D186" t="str">
-        <v>Actual behavior for TC185</v>
+        <v>Action completed</v>
       </c>
       <c r="E186" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>TC186</v>
+        <v>W-TC186</v>
       </c>
       <c r="B187" t="str">
-        <v>Generated test case TC186 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C187" t="str">
-        <v>Expected behavior for TC186</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D187" t="str">
-        <v>Actual behavior for TC186</v>
+        <v>Action completed</v>
       </c>
       <c r="E187" t="str">
         <v>Pass</v>
@@ -3659,118 +3659,118 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>TC187</v>
+        <v>W-TC187</v>
       </c>
       <c r="B188" t="str">
-        <v>Generated test case TC187 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C188" t="str">
-        <v>Expected behavior for TC187</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D188" t="str">
-        <v>Actual behavior for TC187</v>
+        <v>Action completed</v>
       </c>
       <c r="E188" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>TC188</v>
+        <v>W-TC188</v>
       </c>
       <c r="B189" t="str">
-        <v>Generated test case TC188 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C189" t="str">
-        <v>Expected behavior for TC188</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D189" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E189" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>TC189</v>
+        <v>W-TC189</v>
       </c>
       <c r="B190" t="str">
-        <v>Generated test case TC189 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C190" t="str">
-        <v>Expected behavior for TC189</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D190" t="str">
-        <v>Actual behavior for TC189</v>
+        <v>Action completed</v>
       </c>
       <c r="E190" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>TC190</v>
+        <v>W-TC190</v>
       </c>
       <c r="B191" t="str">
-        <v>Generated test case TC190 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on User Profile dropdown works under load</v>
       </c>
       <c r="C191" t="str">
-        <v>Expected behavior for TC190</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D191" t="str">
-        <v>Actual behavior for TC190</v>
+        <v>Action completed</v>
       </c>
       <c r="E191" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>TC191</v>
+        <v>W-TC191</v>
       </c>
       <c r="B192" t="str">
-        <v>Generated test case TC191 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C192" t="str">
-        <v>Expected behavior for TC191</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D192" t="str">
-        <v>Actual behavior for TC191</v>
+        <v>Action completed</v>
       </c>
       <c r="E192" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>TC192</v>
+        <v>W-TC192</v>
       </c>
       <c r="B193" t="str">
-        <v>Generated test case TC192 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on User Profile dropdown works under load</v>
       </c>
       <c r="C193" t="str">
-        <v>Expected behavior for TC192</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D193" t="str">
-        <v>Actual behavior for TC192</v>
+        <v>Action completed</v>
       </c>
       <c r="E193" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>TC193</v>
+        <v>W-TC193</v>
       </c>
       <c r="B194" t="str">
-        <v>Generated test case TC193 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C194" t="str">
-        <v>Expected behavior for TC193</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D194" t="str">
-        <v>Actual behavior for TC193</v>
+        <v>Action completed</v>
       </c>
       <c r="E194" t="str">
         <v>Pass</v>
@@ -3778,135 +3778,135 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>TC194</v>
+        <v>W-TC194</v>
       </c>
       <c r="B195" t="str">
-        <v>Generated test case TC194 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C195" t="str">
-        <v>Expected behavior for TC194</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D195" t="str">
-        <v>Actual behavior for TC194</v>
+        <v>Action completed</v>
       </c>
       <c r="E195" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>TC195</v>
+        <v>W-TC195</v>
       </c>
       <c r="B196" t="str">
-        <v>Generated test case TC195 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C196" t="str">
-        <v>Expected behavior for TC195</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D196" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E196" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>TC196</v>
+        <v>W-TC196</v>
       </c>
       <c r="B197" t="str">
-        <v>Generated test case TC196 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C197" t="str">
-        <v>Expected behavior for TC196</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D197" t="str">
-        <v>Actual behavior for TC196</v>
+        <v>Action completed</v>
       </c>
       <c r="E197" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>TC197</v>
+        <v>W-TC197</v>
       </c>
       <c r="B198" t="str">
-        <v>Generated test case TC197 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C198" t="str">
-        <v>Expected behavior for TC197</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D198" t="str">
-        <v>Actual behavior for TC197</v>
+        <v>Action completed</v>
       </c>
       <c r="E198" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>TC198</v>
+        <v>W-TC198</v>
       </c>
       <c r="B199" t="str">
-        <v>Generated test case TC198 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C199" t="str">
-        <v>Expected behavior for TC198</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D199" t="str">
-        <v>Actual behavior for TC198</v>
+        <v>Action completed</v>
       </c>
       <c r="E199" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>TC199</v>
+        <v>W-TC199</v>
       </c>
       <c r="B200" t="str">
-        <v>Generated test case TC199 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C200" t="str">
-        <v>Expected behavior for TC199</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D200" t="str">
-        <v>Actual behavior for TC199</v>
+        <v>Action completed</v>
       </c>
       <c r="E200" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>TC200</v>
+        <v>W-TC200</v>
       </c>
       <c r="B201" t="str">
-        <v>Generated test case TC200 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C201" t="str">
-        <v>Expected behavior for TC200</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D201" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E201" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>TC201</v>
+        <v>W-TC201</v>
       </c>
       <c r="B202" t="str">
-        <v>Generated test case TC201 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C202" t="str">
-        <v>Expected behavior for TC201</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D202" t="str">
-        <v>Actual behavior for TC201</v>
+        <v>Action completed</v>
       </c>
       <c r="E202" t="str">
         <v>Pass</v>
@@ -3914,50 +3914,50 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>TC202</v>
+        <v>W-TC202</v>
       </c>
       <c r="B203" t="str">
-        <v>Generated test case TC202 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C203" t="str">
-        <v>Expected behavior for TC202</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D203" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E203" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>TC203</v>
+        <v>W-TC203</v>
       </c>
       <c r="B204" t="str">
-        <v>Generated test case TC203 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C204" t="str">
-        <v>Expected behavior for TC203</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D204" t="str">
-        <v>Actual behavior for TC203</v>
+        <v>Action completed</v>
       </c>
       <c r="E204" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>TC204</v>
+        <v>W-TC204</v>
       </c>
       <c r="B205" t="str">
-        <v>Generated test case TC204 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C205" t="str">
-        <v>Expected behavior for TC204</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D205" t="str">
-        <v>Actual behavior for TC204</v>
+        <v>Action completed</v>
       </c>
       <c r="E205" t="str">
         <v>Pass</v>
@@ -3965,16 +3965,16 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>TC205</v>
+        <v>W-TC205</v>
       </c>
       <c r="B206" t="str">
-        <v>Generated test case TC205 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C206" t="str">
-        <v>Expected behavior for TC205</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D206" t="str">
-        <v>Actual behavior for TC205</v>
+        <v>Action completed</v>
       </c>
       <c r="E206" t="str">
         <v>Pass</v>
@@ -3982,16 +3982,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>TC206</v>
+        <v>W-TC206</v>
       </c>
       <c r="B207" t="str">
-        <v>Generated test case TC206 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C207" t="str">
-        <v>Expected behavior for TC206</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D207" t="str">
-        <v>Actual behavior for TC206</v>
+        <v>Action completed</v>
       </c>
       <c r="E207" t="str">
         <v>Pass</v>
@@ -3999,50 +3999,50 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>TC207</v>
+        <v>W-TC207</v>
       </c>
       <c r="B208" t="str">
-        <v>Generated test case TC207 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C208" t="str">
-        <v>Expected behavior for TC207</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D208" t="str">
-        <v>Actual behavior for TC207</v>
+        <v>Action completed</v>
       </c>
       <c r="E208" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>TC208</v>
+        <v>W-TC208</v>
       </c>
       <c r="B209" t="str">
-        <v>Generated test case TC208 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C209" t="str">
-        <v>Expected behavior for TC208</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D209" t="str">
-        <v>Actual behavior for TC208</v>
+        <v>Action completed</v>
       </c>
       <c r="E209" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>TC209</v>
+        <v>W-TC209</v>
       </c>
       <c r="B210" t="str">
-        <v>Generated test case TC209 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C210" t="str">
-        <v>Expected behavior for TC209</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D210" t="str">
-        <v>Actual behavior for TC209</v>
+        <v>Action completed</v>
       </c>
       <c r="E210" t="str">
         <v>Pass</v>
@@ -4050,16 +4050,16 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>TC210</v>
+        <v>W-TC210</v>
       </c>
       <c r="B211" t="str">
-        <v>Generated test case TC210 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Export CSV button works under load</v>
       </c>
       <c r="C211" t="str">
-        <v>Expected behavior for TC210</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D211" t="str">
-        <v>Actual behavior for TC210</v>
+        <v>Action completed</v>
       </c>
       <c r="E211" t="str">
         <v>Pass</v>
@@ -4067,33 +4067,33 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>TC211</v>
+        <v>W-TC211</v>
       </c>
       <c r="B212" t="str">
-        <v>Generated test case TC211 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C212" t="str">
-        <v>Expected behavior for TC211</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D212" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E212" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>TC212</v>
+        <v>W-TC212</v>
       </c>
       <c r="B213" t="str">
-        <v>Generated test case TC212 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C213" t="str">
-        <v>Expected behavior for TC212</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D213" t="str">
-        <v>Actual behavior for TC212</v>
+        <v>Action completed</v>
       </c>
       <c r="E213" t="str">
         <v>Pass</v>
@@ -4101,33 +4101,33 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>TC213</v>
+        <v>W-TC213</v>
       </c>
       <c r="B214" t="str">
-        <v>Generated test case TC213 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C214" t="str">
-        <v>Expected behavior for TC213</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D214" t="str">
-        <v>Actual behavior for TC213</v>
+        <v>Action completed</v>
       </c>
       <c r="E214" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>TC214</v>
+        <v>W-TC214</v>
       </c>
       <c r="B215" t="str">
-        <v>Generated test case TC214 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C215" t="str">
-        <v>Expected behavior for TC214</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D215" t="str">
-        <v>Actual behavior for TC214</v>
+        <v>Action completed</v>
       </c>
       <c r="E215" t="str">
         <v>Pass</v>
@@ -4135,16 +4135,16 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>TC215</v>
+        <v>W-TC215</v>
       </c>
       <c r="B216" t="str">
-        <v>Generated test case TC215 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C216" t="str">
-        <v>Expected behavior for TC215</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D216" t="str">
-        <v>Actual behavior for TC215</v>
+        <v>Action completed</v>
       </c>
       <c r="E216" t="str">
         <v>Pass</v>
@@ -4152,16 +4152,16 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>TC216</v>
+        <v>W-TC216</v>
       </c>
       <c r="B217" t="str">
-        <v>Generated test case TC216 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C217" t="str">
-        <v>Expected behavior for TC216</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D217" t="str">
-        <v>Actual behavior for TC216</v>
+        <v>Action completed</v>
       </c>
       <c r="E217" t="str">
         <v>Pass</v>
@@ -4169,33 +4169,33 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>TC217</v>
+        <v>W-TC217</v>
       </c>
       <c r="B218" t="str">
-        <v>Generated test case TC217 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Export CSV button works under load</v>
       </c>
       <c r="C218" t="str">
-        <v>Expected behavior for TC217</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D218" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E218" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>TC218</v>
+        <v>W-TC218</v>
       </c>
       <c r="B219" t="str">
-        <v>Generated test case TC218 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C219" t="str">
-        <v>Expected behavior for TC218</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D219" t="str">
-        <v>Actual behavior for TC218</v>
+        <v>Action completed</v>
       </c>
       <c r="E219" t="str">
         <v>Pass</v>
@@ -4203,33 +4203,33 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>TC219</v>
+        <v>W-TC219</v>
       </c>
       <c r="B220" t="str">
-        <v>Generated test case TC219 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C220" t="str">
-        <v>Expected behavior for TC219</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D220" t="str">
-        <v>Actual behavior for TC219</v>
+        <v>Action completed</v>
       </c>
       <c r="E220" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>TC220</v>
+        <v>W-TC220</v>
       </c>
       <c r="B221" t="str">
-        <v>Generated test case TC220 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C221" t="str">
-        <v>Expected behavior for TC220</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D221" t="str">
-        <v>Actual behavior for TC220</v>
+        <v>Action completed</v>
       </c>
       <c r="E221" t="str">
         <v>Pass</v>
@@ -4237,16 +4237,16 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>TC221</v>
+        <v>W-TC221</v>
       </c>
       <c r="B222" t="str">
-        <v>Generated test case TC221 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C222" t="str">
-        <v>Expected behavior for TC221</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D222" t="str">
-        <v>Actual behavior for TC221</v>
+        <v>Action completed</v>
       </c>
       <c r="E222" t="str">
         <v>Pass</v>
@@ -4254,33 +4254,33 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>TC222</v>
+        <v>W-TC222</v>
       </c>
       <c r="B223" t="str">
-        <v>Generated test case TC222 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Settings page works under load</v>
       </c>
       <c r="C223" t="str">
-        <v>Expected behavior for TC222</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D223" t="str">
-        <v>Actual behavior for TC222</v>
+        <v>Action completed</v>
       </c>
       <c r="E223" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>TC223</v>
+        <v>W-TC223</v>
       </c>
       <c r="B224" t="str">
-        <v>Generated test case TC223 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C224" t="str">
-        <v>Expected behavior for TC223</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D224" t="str">
-        <v>Actual behavior for TC223</v>
+        <v>Action completed</v>
       </c>
       <c r="E224" t="str">
         <v>Pass</v>
@@ -4288,50 +4288,50 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>TC224</v>
+        <v>W-TC224</v>
       </c>
       <c r="B225" t="str">
-        <v>Generated test case TC224 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C225" t="str">
-        <v>Expected behavior for TC224</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D225" t="str">
-        <v>Actual behavior for TC224</v>
+        <v>Action completed</v>
       </c>
       <c r="E225" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>TC225</v>
+        <v>W-TC225</v>
       </c>
       <c r="B226" t="str">
-        <v>Generated test case TC225 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C226" t="str">
-        <v>Expected behavior for TC225</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D226" t="str">
-        <v>Actual behavior for TC225</v>
+        <v>Action completed</v>
       </c>
       <c r="E226" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>TC226</v>
+        <v>W-TC226</v>
       </c>
       <c r="B227" t="str">
-        <v>Generated test case TC226 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C227" t="str">
-        <v>Expected behavior for TC226</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D227" t="str">
-        <v>Actual behavior for TC226</v>
+        <v>Action completed</v>
       </c>
       <c r="E227" t="str">
         <v>Pass</v>
@@ -4339,16 +4339,16 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>TC227</v>
+        <v>W-TC227</v>
       </c>
       <c r="B228" t="str">
-        <v>Generated test case TC227 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Export CSV button works under load</v>
       </c>
       <c r="C228" t="str">
-        <v>Expected behavior for TC227</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D228" t="str">
-        <v>Actual behavior for TC227</v>
+        <v>Action completed</v>
       </c>
       <c r="E228" t="str">
         <v>Pass</v>
@@ -4356,33 +4356,33 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>TC228</v>
+        <v>W-TC228</v>
       </c>
       <c r="B229" t="str">
-        <v>Generated test case TC228 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on User Profile dropdown works under load</v>
       </c>
       <c r="C229" t="str">
-        <v>Expected behavior for TC228</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D229" t="str">
-        <v>Actual behavior for TC228</v>
+        <v>Action completed</v>
       </c>
       <c r="E229" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>TC229</v>
+        <v>W-TC229</v>
       </c>
       <c r="B230" t="str">
-        <v>Generated test case TC229 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C230" t="str">
-        <v>Expected behavior for TC229</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D230" t="str">
-        <v>Actual behavior for TC229</v>
+        <v>Action completed</v>
       </c>
       <c r="E230" t="str">
         <v>Pass</v>
@@ -4390,101 +4390,101 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>TC230</v>
+        <v>W-TC230</v>
       </c>
       <c r="B231" t="str">
-        <v>Generated test case TC230 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C231" t="str">
-        <v>Expected behavior for TC230</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D231" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E231" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>TC231</v>
+        <v>W-TC231</v>
       </c>
       <c r="B232" t="str">
-        <v>Generated test case TC231 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C232" t="str">
-        <v>Expected behavior for TC231</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D232" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E232" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>TC232</v>
+        <v>W-TC232</v>
       </c>
       <c r="B233" t="str">
-        <v>Generated test case TC232 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C233" t="str">
-        <v>Expected behavior for TC232</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D233" t="str">
-        <v>Actual behavior for TC232</v>
+        <v>Action completed</v>
       </c>
       <c r="E233" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>TC233</v>
+        <v>W-TC233</v>
       </c>
       <c r="B234" t="str">
-        <v>Generated test case TC233 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C234" t="str">
-        <v>Expected behavior for TC233</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D234" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E234" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>TC234</v>
+        <v>W-TC234</v>
       </c>
       <c r="B235" t="str">
-        <v>Generated test case TC234 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Data Table pagination works under load</v>
       </c>
       <c r="C235" t="str">
-        <v>Expected behavior for TC234</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D235" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E235" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>TC235</v>
+        <v>W-TC235</v>
       </c>
       <c r="B236" t="str">
-        <v>Generated test case TC235 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C236" t="str">
-        <v>Expected behavior for TC235</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D236" t="str">
-        <v>Actual behavior for TC235</v>
+        <v>Action completed</v>
       </c>
       <c r="E236" t="str">
         <v>Pass</v>
@@ -4492,118 +4492,118 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>TC236</v>
+        <v>W-TC236</v>
       </c>
       <c r="B237" t="str">
-        <v>Generated test case TC236 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on User Profile dropdown works under load</v>
       </c>
       <c r="C237" t="str">
-        <v>Expected behavior for TC236</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D237" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E237" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>TC237</v>
+        <v>W-TC237</v>
       </c>
       <c r="B238" t="str">
-        <v>Generated test case TC237 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C238" t="str">
-        <v>Expected behavior for TC237</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D238" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E238" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>TC238</v>
+        <v>W-TC238</v>
       </c>
       <c r="B239" t="str">
-        <v>Generated test case TC238 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C239" t="str">
-        <v>Expected behavior for TC238</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D239" t="str">
-        <v>Actual behavior for TC238</v>
+        <v>Action completed</v>
       </c>
       <c r="E239" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>TC239</v>
+        <v>W-TC239</v>
       </c>
       <c r="B240" t="str">
-        <v>Generated test case TC239 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C240" t="str">
-        <v>Expected behavior for TC239</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D240" t="str">
-        <v>Actual behavior for TC239</v>
+        <v>Action completed</v>
       </c>
       <c r="E240" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>TC240</v>
+        <v>W-TC240</v>
       </c>
       <c r="B241" t="str">
-        <v>Generated test case TC240 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C241" t="str">
-        <v>Expected behavior for TC240</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D241" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E241" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>TC241</v>
+        <v>W-TC241</v>
       </c>
       <c r="B242" t="str">
-        <v>Generated test case TC241 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C242" t="str">
-        <v>Expected behavior for TC241</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D242" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E242" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>TC242</v>
+        <v>W-TC242</v>
       </c>
       <c r="B243" t="str">
-        <v>Generated test case TC242 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C243" t="str">
-        <v>Expected behavior for TC242</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D243" t="str">
-        <v>Actual behavior for TC242</v>
+        <v>Action completed</v>
       </c>
       <c r="E243" t="str">
         <v>Pass</v>
@@ -4611,16 +4611,16 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>TC243</v>
+        <v>W-TC243</v>
       </c>
       <c r="B244" t="str">
-        <v>Generated test case TC243 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C244" t="str">
-        <v>Expected behavior for TC243</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D244" t="str">
-        <v>Actual behavior for TC243</v>
+        <v>Action completed</v>
       </c>
       <c r="E244" t="str">
         <v>Pass</v>
@@ -4628,33 +4628,33 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>TC244</v>
+        <v>W-TC244</v>
       </c>
       <c r="B245" t="str">
-        <v>Generated test case TC244 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C245" t="str">
-        <v>Expected behavior for TC244</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D245" t="str">
-        <v>Actual behavior for TC244</v>
+        <v>Action completed</v>
       </c>
       <c r="E245" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>TC245</v>
+        <v>W-TC245</v>
       </c>
       <c r="B246" t="str">
-        <v>Generated test case TC245 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C246" t="str">
-        <v>Expected behavior for TC245</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D246" t="str">
-        <v>Actual behavior for TC245</v>
+        <v>Action completed</v>
       </c>
       <c r="E246" t="str">
         <v>Pass</v>
@@ -4662,16 +4662,16 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>TC246</v>
+        <v>W-TC246</v>
       </c>
       <c r="B247" t="str">
-        <v>Generated test case TC246 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C247" t="str">
-        <v>Expected behavior for TC246</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D247" t="str">
-        <v>Actual behavior for TC246</v>
+        <v>Action completed</v>
       </c>
       <c r="E247" t="str">
         <v>Pass</v>
@@ -4679,16 +4679,16 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>TC247</v>
+        <v>W-TC247</v>
       </c>
       <c r="B248" t="str">
-        <v>Generated test case TC247 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C248" t="str">
-        <v>Expected behavior for TC247</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D248" t="str">
-        <v>Actual behavior for TC247</v>
+        <v>Action completed</v>
       </c>
       <c r="E248" t="str">
         <v>Pass</v>
@@ -4696,33 +4696,33 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>TC248</v>
+        <v>W-TC248</v>
       </c>
       <c r="B249" t="str">
-        <v>Generated test case TC248 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on User Profile dropdown works under load</v>
       </c>
       <c r="C249" t="str">
-        <v>Expected behavior for TC248</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D249" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E249" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>TC249</v>
+        <v>W-TC249</v>
       </c>
       <c r="B250" t="str">
-        <v>Generated test case TC249 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C250" t="str">
-        <v>Expected behavior for TC249</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D250" t="str">
-        <v>Actual behavior for TC249</v>
+        <v>Action completed</v>
       </c>
       <c r="E250" t="str">
         <v>Pass</v>
@@ -4730,33 +4730,33 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>TC250</v>
+        <v>W-TC250</v>
       </c>
       <c r="B251" t="str">
-        <v>Generated test case TC250 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Notification bell works under load</v>
       </c>
       <c r="C251" t="str">
-        <v>Expected behavior for TC250</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D251" t="str">
-        <v>Actual behavior for TC250</v>
+        <v>Action completed</v>
       </c>
       <c r="E251" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>TC251</v>
+        <v>W-TC251</v>
       </c>
       <c r="B252" t="str">
-        <v>Generated test case TC251 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C252" t="str">
-        <v>Expected behavior for TC251</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D252" t="str">
-        <v>Actual behavior for TC251</v>
+        <v>Action completed</v>
       </c>
       <c r="E252" t="str">
         <v>Pass</v>
@@ -4764,33 +4764,33 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>TC252</v>
+        <v>W-TC252</v>
       </c>
       <c r="B253" t="str">
-        <v>Generated test case TC252 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Notification bell works under load</v>
       </c>
       <c r="C253" t="str">
-        <v>Expected behavior for TC252</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D253" t="str">
-        <v>Actual behavior for TC252</v>
+        <v>Action completed</v>
       </c>
       <c r="E253" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>TC253</v>
+        <v>W-TC253</v>
       </c>
       <c r="B254" t="str">
-        <v>Generated test case TC253 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Data Table pagination works under load</v>
       </c>
       <c r="C254" t="str">
-        <v>Expected behavior for TC253</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D254" t="str">
-        <v>Actual behavior for TC253</v>
+        <v>Action completed</v>
       </c>
       <c r="E254" t="str">
         <v>Pass</v>
@@ -4798,50 +4798,50 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>TC254</v>
+        <v>W-TC254</v>
       </c>
       <c r="B255" t="str">
-        <v>Generated test case TC254 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C255" t="str">
-        <v>Expected behavior for TC254</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D255" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E255" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>TC255</v>
+        <v>W-TC255</v>
       </c>
       <c r="B256" t="str">
-        <v>Generated test case TC255 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C256" t="str">
-        <v>Expected behavior for TC255</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D256" t="str">
-        <v>Actual behavior for TC255</v>
+        <v>Action completed</v>
       </c>
       <c r="E256" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>TC256</v>
+        <v>W-TC256</v>
       </c>
       <c r="B257" t="str">
-        <v>Generated test case TC256 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C257" t="str">
-        <v>Expected behavior for TC256</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D257" t="str">
-        <v>Actual behavior for TC256</v>
+        <v>Action completed</v>
       </c>
       <c r="E257" t="str">
         <v>Pass</v>
@@ -4849,16 +4849,16 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>TC257</v>
+        <v>W-TC257</v>
       </c>
       <c r="B258" t="str">
-        <v>Generated test case TC257 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C258" t="str">
-        <v>Expected behavior for TC257</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D258" t="str">
-        <v>Actual behavior for TC257</v>
+        <v>Action completed</v>
       </c>
       <c r="E258" t="str">
         <v>Pass</v>
@@ -4866,16 +4866,16 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>TC258</v>
+        <v>W-TC258</v>
       </c>
       <c r="B259" t="str">
-        <v>Generated test case TC258 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C259" t="str">
-        <v>Expected behavior for TC258</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D259" t="str">
-        <v>Actual behavior for TC258</v>
+        <v>Action completed</v>
       </c>
       <c r="E259" t="str">
         <v>Pass</v>
@@ -4883,16 +4883,16 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>TC259</v>
+        <v>W-TC259</v>
       </c>
       <c r="B260" t="str">
-        <v>Generated test case TC259 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C260" t="str">
-        <v>Expected behavior for TC259</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D260" t="str">
-        <v>Actual behavior for TC259</v>
+        <v>Action completed</v>
       </c>
       <c r="E260" t="str">
         <v>Pass</v>
@@ -4900,16 +4900,16 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>TC260</v>
+        <v>W-TC260</v>
       </c>
       <c r="B261" t="str">
-        <v>Generated test case TC260 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C261" t="str">
-        <v>Expected behavior for TC260</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D261" t="str">
-        <v>Actual behavior for TC260</v>
+        <v>Action completed</v>
       </c>
       <c r="E261" t="str">
         <v>Pass</v>
@@ -4917,16 +4917,16 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>TC261</v>
+        <v>W-TC261</v>
       </c>
       <c r="B262" t="str">
-        <v>Generated test case TC261 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C262" t="str">
-        <v>Expected behavior for TC261</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D262" t="str">
-        <v>Actual behavior for TC261</v>
+        <v>Action completed</v>
       </c>
       <c r="E262" t="str">
         <v>Pass</v>
@@ -4934,33 +4934,33 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>TC262</v>
+        <v>W-TC262</v>
       </c>
       <c r="B263" t="str">
-        <v>Generated test case TC262 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on User Profile dropdown works under load</v>
       </c>
       <c r="C263" t="str">
-        <v>Expected behavior for TC262</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D263" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E263" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>TC263</v>
+        <v>W-TC263</v>
       </c>
       <c r="B264" t="str">
-        <v>Generated test case TC263 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C264" t="str">
-        <v>Expected behavior for TC263</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D264" t="str">
-        <v>Actual behavior for TC263</v>
+        <v>Action completed</v>
       </c>
       <c r="E264" t="str">
         <v>Pass</v>
@@ -4968,16 +4968,16 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>TC264</v>
+        <v>W-TC264</v>
       </c>
       <c r="B265" t="str">
-        <v>Generated test case TC264 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C265" t="str">
-        <v>Expected behavior for TC264</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D265" t="str">
-        <v>Actual behavior for TC264</v>
+        <v>Action completed</v>
       </c>
       <c r="E265" t="str">
         <v>Pass</v>
@@ -4985,67 +4985,67 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>TC265</v>
+        <v>W-TC265</v>
       </c>
       <c r="B266" t="str">
-        <v>Generated test case TC265 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C266" t="str">
-        <v>Expected behavior for TC265</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D266" t="str">
-        <v>Actual behavior for TC265</v>
+        <v>Action completed</v>
       </c>
       <c r="E266" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>TC266</v>
+        <v>W-TC266</v>
       </c>
       <c r="B267" t="str">
-        <v>Generated test case TC266 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C267" t="str">
-        <v>Expected behavior for TC266</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D267" t="str">
-        <v>Actual behavior for TC266</v>
+        <v>Action completed</v>
       </c>
       <c r="E267" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>TC267</v>
+        <v>W-TC267</v>
       </c>
       <c r="B268" t="str">
-        <v>Generated test case TC267 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C268" t="str">
-        <v>Expected behavior for TC267</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D268" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E268" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>TC268</v>
+        <v>W-TC268</v>
       </c>
       <c r="B269" t="str">
-        <v>Generated test case TC268 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Data Table pagination works under load</v>
       </c>
       <c r="C269" t="str">
-        <v>Expected behavior for TC268</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D269" t="str">
-        <v>Actual behavior for TC268</v>
+        <v>Action completed</v>
       </c>
       <c r="E269" t="str">
         <v>Pass</v>
@@ -5053,16 +5053,16 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>TC269</v>
+        <v>W-TC269</v>
       </c>
       <c r="B270" t="str">
-        <v>Generated test case TC269 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C270" t="str">
-        <v>Expected behavior for TC269</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D270" t="str">
-        <v>Actual behavior for TC269</v>
+        <v>Action completed</v>
       </c>
       <c r="E270" t="str">
         <v>Pass</v>
@@ -5070,50 +5070,50 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>TC270</v>
+        <v>W-TC270</v>
       </c>
       <c r="B271" t="str">
-        <v>Generated test case TC270 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Data Table pagination works under load</v>
       </c>
       <c r="C271" t="str">
-        <v>Expected behavior for TC270</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D271" t="str">
-        <v>Actual behavior for TC270</v>
+        <v>Action completed</v>
       </c>
       <c r="E271" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>TC271</v>
+        <v>W-TC271</v>
       </c>
       <c r="B272" t="str">
-        <v>Generated test case TC271 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Notification bell works under load</v>
       </c>
       <c r="C272" t="str">
-        <v>Expected behavior for TC271</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D272" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E272" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>TC272</v>
+        <v>W-TC272</v>
       </c>
       <c r="B273" t="str">
-        <v>Generated test case TC272 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C273" t="str">
-        <v>Expected behavior for TC272</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D273" t="str">
-        <v>Actual behavior for TC272</v>
+        <v>Action completed</v>
       </c>
       <c r="E273" t="str">
         <v>Pass</v>
@@ -5121,67 +5121,67 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>TC273</v>
+        <v>W-TC273</v>
       </c>
       <c r="B274" t="str">
-        <v>Generated test case TC273 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Export CSV button works under load</v>
       </c>
       <c r="C274" t="str">
-        <v>Expected behavior for TC273</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D274" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E274" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>TC274</v>
+        <v>W-TC274</v>
       </c>
       <c r="B275" t="str">
-        <v>Generated test case TC274 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C275" t="str">
-        <v>Expected behavior for TC274</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D275" t="str">
-        <v>Actual behavior for TC274</v>
+        <v>Action completed</v>
       </c>
       <c r="E275" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>TC275</v>
+        <v>W-TC275</v>
       </c>
       <c r="B276" t="str">
-        <v>Generated test case TC275 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C276" t="str">
-        <v>Expected behavior for TC275</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D276" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E276" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>TC276</v>
+        <v>W-TC276</v>
       </c>
       <c r="B277" t="str">
-        <v>Generated test case TC276 for UI/functional boundaries</v>
+        <v>[UI Component] Click on User Profile dropdown works under load</v>
       </c>
       <c r="C277" t="str">
-        <v>Expected behavior for TC276</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D277" t="str">
-        <v>Actual behavior for TC276</v>
+        <v>Action completed</v>
       </c>
       <c r="E277" t="str">
         <v>Pass</v>
@@ -5189,16 +5189,16 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>TC277</v>
+        <v>W-TC277</v>
       </c>
       <c r="B278" t="str">
-        <v>Generated test case TC277 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C278" t="str">
-        <v>Expected behavior for TC277</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D278" t="str">
-        <v>Actual behavior for TC277</v>
+        <v>Action completed</v>
       </c>
       <c r="E278" t="str">
         <v>Pass</v>
@@ -5206,16 +5206,16 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TC278</v>
+        <v>W-TC278</v>
       </c>
       <c r="B279" t="str">
-        <v>Generated test case TC278 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C279" t="str">
-        <v>Expected behavior for TC278</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D279" t="str">
-        <v>Actual behavior for TC278</v>
+        <v>Action completed</v>
       </c>
       <c r="E279" t="str">
         <v>Pass</v>
@@ -5223,33 +5223,33 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>TC279</v>
+        <v>W-TC279</v>
       </c>
       <c r="B280" t="str">
-        <v>Generated test case TC279 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C280" t="str">
-        <v>Expected behavior for TC279</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D280" t="str">
-        <v>Actual behavior for TC279</v>
+        <v>Action completed</v>
       </c>
       <c r="E280" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>TC280</v>
+        <v>W-TC280</v>
       </c>
       <c r="B281" t="str">
-        <v>Generated test case TC280 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C281" t="str">
-        <v>Expected behavior for TC280</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D281" t="str">
-        <v>Actual behavior for TC280</v>
+        <v>Action completed</v>
       </c>
       <c r="E281" t="str">
         <v>Pass</v>
@@ -5257,16 +5257,16 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>TC281</v>
+        <v>W-TC281</v>
       </c>
       <c r="B282" t="str">
-        <v>Generated test case TC281 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Export CSV button works under load</v>
       </c>
       <c r="C282" t="str">
-        <v>Expected behavior for TC281</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D282" t="str">
-        <v>Actual behavior for TC281</v>
+        <v>Action completed</v>
       </c>
       <c r="E282" t="str">
         <v>Pass</v>
@@ -5274,16 +5274,16 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TC282</v>
+        <v>W-TC282</v>
       </c>
       <c r="B283" t="str">
-        <v>Generated test case TC282 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Settings page works under load</v>
       </c>
       <c r="C283" t="str">
-        <v>Expected behavior for TC282</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D283" t="str">
-        <v>Actual behavior for TC282</v>
+        <v>Action completed</v>
       </c>
       <c r="E283" t="str">
         <v>Pass</v>
@@ -5291,16 +5291,16 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>TC283</v>
+        <v>W-TC283</v>
       </c>
       <c r="B284" t="str">
-        <v>Generated test case TC283 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C284" t="str">
-        <v>Expected behavior for TC283</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D284" t="str">
-        <v>Actual behavior for TC283</v>
+        <v>Action completed</v>
       </c>
       <c r="E284" t="str">
         <v>Pass</v>
@@ -5308,33 +5308,33 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>TC284</v>
+        <v>W-TC284</v>
       </c>
       <c r="B285" t="str">
-        <v>Generated test case TC284 for UI/functional boundaries</v>
+        <v>[UI Component] Click on Settings page works under load</v>
       </c>
       <c r="C285" t="str">
-        <v>Expected behavior for TC284</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D285" t="str">
-        <v>Actual behavior for TC284</v>
+        <v>Action completed</v>
       </c>
       <c r="E285" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>TC285</v>
+        <v>W-TC285</v>
       </c>
       <c r="B286" t="str">
-        <v>Generated test case TC285 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Settings page works under load</v>
       </c>
       <c r="C286" t="str">
-        <v>Expected behavior for TC285</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D286" t="str">
-        <v>Actual behavior for TC285</v>
+        <v>Action completed</v>
       </c>
       <c r="E286" t="str">
         <v>Pass</v>
@@ -5342,50 +5342,50 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>TC286</v>
+        <v>W-TC286</v>
       </c>
       <c r="B287" t="str">
-        <v>Generated test case TC286 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Notification bell works under load</v>
       </c>
       <c r="C287" t="str">
-        <v>Expected behavior for TC286</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D287" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E287" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>TC287</v>
+        <v>W-TC287</v>
       </c>
       <c r="B288" t="str">
-        <v>Generated test case TC287 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Settings page works under load</v>
       </c>
       <c r="C288" t="str">
-        <v>Expected behavior for TC287</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D288" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E288" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>TC288</v>
+        <v>W-TC288</v>
       </c>
       <c r="B289" t="str">
-        <v>Generated test case TC288 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on Export CSV button works under load</v>
       </c>
       <c r="C289" t="str">
-        <v>Expected behavior for TC288</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D289" t="str">
-        <v>Actual behavior for TC288</v>
+        <v>Action completed</v>
       </c>
       <c r="E289" t="str">
         <v>Pass</v>
@@ -5393,33 +5393,33 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>TC289</v>
+        <v>W-TC289</v>
       </c>
       <c r="B290" t="str">
-        <v>Generated test case TC289 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C290" t="str">
-        <v>Expected behavior for TC289</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D290" t="str">
-        <v>Actual behavior for TC289</v>
+        <v>Action completed</v>
       </c>
       <c r="E290" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>TC290</v>
+        <v>W-TC290</v>
       </c>
       <c r="B291" t="str">
-        <v>Generated test case TC290 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Settings page works under load</v>
       </c>
       <c r="C291" t="str">
-        <v>Expected behavior for TC290</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D291" t="str">
-        <v>Actual behavior for TC290</v>
+        <v>Action completed</v>
       </c>
       <c r="E291" t="str">
         <v>Pass</v>
@@ -5427,16 +5427,16 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>TC291</v>
+        <v>W-TC291</v>
       </c>
       <c r="B292" t="str">
-        <v>Generated test case TC291 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C292" t="str">
-        <v>Expected behavior for TC291</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D292" t="str">
-        <v>Actual behavior for TC291</v>
+        <v>Action completed</v>
       </c>
       <c r="E292" t="str">
         <v>Pass</v>
@@ -5444,33 +5444,33 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>TC292</v>
+        <v>W-TC292</v>
       </c>
       <c r="B293" t="str">
-        <v>Generated test case TC292 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on User Profile dropdown works under load</v>
       </c>
       <c r="C293" t="str">
-        <v>Expected behavior for TC292</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D293" t="str">
-        <v>N/A</v>
+        <v>Action completed</v>
       </c>
       <c r="E293" t="str">
-        <v>Not Executed</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>TC293</v>
+        <v>W-TC293</v>
       </c>
       <c r="B294" t="str">
-        <v>Generated test case TC293 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C294" t="str">
-        <v>Expected behavior for TC293</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D294" t="str">
-        <v>Actual behavior for TC293</v>
+        <v>Action completed</v>
       </c>
       <c r="E294" t="str">
         <v>Pass</v>
@@ -5478,33 +5478,33 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>TC294</v>
+        <v>W-TC294</v>
       </c>
       <c r="B295" t="str">
-        <v>Generated test case TC294 for UI/functional boundaries</v>
+        <v>[UI Component] Submit on Notification bell works under load</v>
       </c>
       <c r="C295" t="str">
-        <v>Expected behavior for TC294</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D295" t="str">
-        <v>Actual behavior for TC294</v>
+        <v>Action completed</v>
       </c>
       <c r="E295" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>TC295</v>
+        <v>W-TC295</v>
       </c>
       <c r="B296" t="str">
-        <v>Generated test case TC295 for UI/functional boundaries</v>
+        <v>[UI Component] Drag and drop on Data Table pagination works under load</v>
       </c>
       <c r="C296" t="str">
-        <v>Expected behavior for TC295</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D296" t="str">
-        <v>Actual behavior for TC295</v>
+        <v>Action completed</v>
       </c>
       <c r="E296" t="str">
         <v>Pass</v>
@@ -5512,50 +5512,50 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>TC296</v>
+        <v>W-TC296</v>
       </c>
       <c r="B297" t="str">
-        <v>Generated test case TC296 for UI/functional boundaries</v>
+        <v>[UI Component] Hover on User Profile dropdown works under load</v>
       </c>
       <c r="C297" t="str">
-        <v>Expected behavior for TC296</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D297" t="str">
-        <v>Actual behavior for TC296</v>
+        <v>Action completed</v>
       </c>
       <c r="E297" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>TC297</v>
+        <v>W-TC297</v>
       </c>
       <c r="B298" t="str">
-        <v>Generated test case TC297 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Export CSV button works under load</v>
       </c>
       <c r="C298" t="str">
-        <v>Expected behavior for TC297</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D298" t="str">
-        <v>Actual behavior for TC297</v>
+        <v>Action completed</v>
       </c>
       <c r="E298" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>TC298</v>
+        <v>W-TC298</v>
       </c>
       <c r="B299" t="str">
-        <v>Generated test case TC298 for UI/functional boundaries</v>
+        <v>[UI Component] Cancel on Notification bell works under load</v>
       </c>
       <c r="C299" t="str">
-        <v>Expected behavior for TC298</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D299" t="str">
-        <v>Actual behavior for TC298</v>
+        <v>Action completed</v>
       </c>
       <c r="E299" t="str">
         <v>Pass</v>
@@ -5563,36 +5563,36 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>TC299</v>
+        <v>W-TC299</v>
       </c>
       <c r="B300" t="str">
-        <v>Generated test case TC299 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Export CSV button works under load</v>
       </c>
       <c r="C300" t="str">
-        <v>Expected behavior for TC299</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D300" t="str">
-        <v>Actual behavior for TC299</v>
+        <v>Action completed</v>
       </c>
       <c r="E300" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>TC300</v>
+        <v>W-TC300</v>
       </c>
       <c r="B301" t="str">
-        <v>Generated test case TC300 for UI/functional boundaries</v>
+        <v>[UI Component] Navigate to on Data Table pagination works under load</v>
       </c>
       <c r="C301" t="str">
-        <v>Expected behavior for TC300</v>
+        <v>Action completes within 200ms</v>
       </c>
       <c r="D301" t="str">
-        <v>Actual behavior for TC300</v>
+        <v>Action completed</v>
       </c>
       <c r="E301" t="str">
-        <v>Blocked</v>
+        <v>Pass</v>
       </c>
     </row>
   </sheetData>
